--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -522,11 +522,11 @@
         <v>-10000</v>
       </c>
       <c r="K2" t="n">
-        <v>20990</v>
+        <v>32990</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-147.6%</t>
+          <t>-130.3%</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-16900</v>
+        <v>-10900</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -902,47 +902,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>姜人荷</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="D10" t="n">
-        <v>26400</v>
+        <v>48260</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-42.1%</t>
+          <t>+274.5%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>18774</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+56.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>26400</v>
+        <v>29486</v>
       </c>
       <c r="K10" t="n">
-        <v>45600</v>
+        <v>876</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-42.1%</t>
+          <t>+3266.0%</t>
         </is>
       </c>
     </row>
@@ -954,47 +954,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>姜人荷</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>48260</v>
+        <v>53220</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+274.5%</t>
+          <t>+16.7%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>18774</v>
+        <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>+56.3%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>29486</v>
+        <v>53220</v>
       </c>
       <c r="K11" t="n">
-        <v>876</v>
+        <v>40100</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+3266.0%</t>
+          <t>+32.7%</t>
         </is>
       </c>
     </row>
@@ -1013,11 +1013,11 @@
         <v>110000</v>
       </c>
       <c r="D12" t="n">
-        <v>46200</v>
+        <v>66000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1039,14 +1039,14 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>21400</v>
+        <v>41200</v>
       </c>
       <c r="K12" t="n">
         <v>-27218</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-178.6%</t>
+          <t>-251.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+828.5%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1094,11 +1094,11 @@
         <v>61280</v>
       </c>
       <c r="K13" t="n">
-        <v>-10000</v>
+        <v>-3400</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-712.8%</t>
+          <t>-1902.4%</t>
         </is>
       </c>
     </row>
@@ -1130,27 +1130,27 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4183</v>
+        <v>54103</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-91.8%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>54637</v>
+        <v>4717</v>
       </c>
       <c r="K14" t="n">
-        <v>49751.34</v>
+        <v>48071.34</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+9.8%</t>
+          <t>-90.2%</t>
         </is>
       </c>
     </row>
@@ -1295,18 +1295,18 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-85.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
         <v>11741.9</v>
       </c>
       <c r="K17" t="n">
-        <v>19670.69</v>
+        <v>17081.69</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-40.3%</t>
+          <t>-31.3%</t>
         </is>
       </c>
     </row>
@@ -1481,16 +1481,16 @@
         <v>40000</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-60.0%</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1507,14 +1507,14 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="K21" t="n">
         <v>9960</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-60.0%</t>
         </is>
       </c>
     </row>
@@ -1555,18 +1555,18 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>+77.2%</t>
+          <t>+24.9%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>-13720</v>
       </c>
       <c r="K22" t="n">
-        <v>1593.34</v>
+        <v>-2589.66</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-961.1%</t>
+          <t>+429.8%</t>
         </is>
       </c>
     </row>
@@ -1630,47 +1630,47 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>130000</v>
+        <v>150000</v>
       </c>
       <c r="D24" t="n">
-        <v>9640</v>
+        <v>19900</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-67.7%</t>
+          <t>-42.9%</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-68.3%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>9640</v>
+        <v>14920</v>
       </c>
       <c r="K24" t="n">
-        <v>25898</v>
+        <v>19126.26</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-62.8%</t>
+          <t>-22.0%</t>
         </is>
       </c>
     </row>
@@ -1689,16 +1689,16 @@
         <v>160000</v>
       </c>
       <c r="D25" t="n">
-        <v>11940</v>
+        <v>23880</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-68.7%</t>
+          <t>-37.4%</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1715,14 +1715,14 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>5190</v>
+        <v>17130</v>
       </c>
       <c r="K25" t="n">
         <v>19833.67</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-13.6%</t>
         </is>
       </c>
     </row>
@@ -1741,16 +1741,16 @@
         <v>100000</v>
       </c>
       <c r="D26" t="n">
-        <v>7960</v>
+        <v>15920</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>+41.1%</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1767,14 +1767,14 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>7960</v>
+        <v>15920</v>
       </c>
       <c r="K26" t="n">
-        <v>6260</v>
+        <v>6299</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+27.2%</t>
+          <t>+152.7%</t>
         </is>
       </c>
     </row>
@@ -1786,47 +1786,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>150000</v>
+        <v>130000</v>
       </c>
       <c r="D27" t="n">
-        <v>19900</v>
+        <v>21580</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-46.3%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-68.3%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>14920</v>
+        <v>21580</v>
       </c>
       <c r="K27" t="n">
-        <v>14146.26</v>
+        <v>36198</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+5.5%</t>
+          <t>-40.4%</t>
         </is>
       </c>
     </row>
@@ -1845,16 +1845,16 @@
         <v>130000</v>
       </c>
       <c r="D28" t="n">
-        <v>65540</v>
+        <v>69520</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+392.1%</t>
+          <t>+422.0%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1871,14 +1871,14 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>65142</v>
+        <v>69122</v>
       </c>
       <c r="K28" t="n">
         <v>13318</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+389.1%</t>
+          <t>+419.0%</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-98.6%</t>
+          <t>-98.7%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1978,11 +1978,11 @@
         <v>-64334</v>
       </c>
       <c r="K30" t="n">
-        <v>126974</v>
+        <v>132656</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-150.7%</t>
+          <t>-148.5%</t>
         </is>
       </c>
     </row>
@@ -2030,11 +2030,11 @@
         <v>19800</v>
       </c>
       <c r="K31" t="n">
-        <v>128603.5</v>
+        <v>123653.5</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-84.6%</t>
+          <t>-84.0%</t>
         </is>
       </c>
     </row>
@@ -2105,11 +2105,11 @@
         <v>70000</v>
       </c>
       <c r="D33" t="n">
-        <v>3980</v>
+        <v>5874</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2118,11 +2118,11 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>3980</v>
+        <v>894</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2150,23 +2150,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>王蓉</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>9560</v>
+        <v>7768</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+141.4%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2179,18 +2179,18 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>9560</v>
+        <v>7768</v>
       </c>
       <c r="K34" t="n">
-        <v>-3199</v>
+        <v>0</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-398.8%</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
@@ -2202,47 +2202,47 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>王蓉</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>80000</v>
+        <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>7768</v>
+        <v>17520</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+131.7%</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>7768</v>
+        <v>13920</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+3371.3%</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>闫文奇</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2270,31 +2270,31 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+57.6%</t>
+          <t>+215.2%</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+79.1%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>11940</v>
+        <v>6960</v>
       </c>
       <c r="K36" t="n">
-        <v>7576</v>
+        <v>1007</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+57.6%</t>
+          <t>+591.2%</t>
         </is>
       </c>
     </row>
@@ -2306,31 +2306,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>闫文奇</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>80000</v>
       </c>
       <c r="D37" t="n">
-        <v>11940</v>
+        <v>15920</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+215.2%</t>
+          <t>+110.1%</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2339,14 +2339,14 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>6960</v>
+        <v>15920</v>
       </c>
       <c r="K37" t="n">
-        <v>3788</v>
+        <v>7576</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+83.7%</t>
+          <t>+110.1%</t>
         </is>
       </c>
     </row>
@@ -2365,11 +2365,11 @@
         <v>80000</v>
       </c>
       <c r="D38" t="n">
-        <v>19900</v>
+        <v>23880</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>17303.4</v>
+        <v>21283.4</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2469,16 +2469,16 @@
         <v>200000</v>
       </c>
       <c r="D40" t="n">
-        <v>4180</v>
+        <v>34180</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-93.1%</t>
+          <t>-43.8%</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>712.9%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2495,14 +2495,14 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>-25620</v>
+        <v>4380</v>
       </c>
       <c r="K40" t="n">
         <v>54320</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-147.2%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
@@ -2521,16 +2521,16 @@
         <v>250000</v>
       </c>
       <c r="D41" t="n">
-        <v>57570</v>
+        <v>49570</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-45.9%</t>
+          <t>-53.4%</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2547,14 +2547,14 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>50370</v>
+        <v>42370</v>
       </c>
       <c r="K41" t="n">
         <v>97840</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-56.7%</t>
         </is>
       </c>
     </row>
@@ -2573,16 +2573,16 @@
         <v>100000</v>
       </c>
       <c r="D42" t="n">
-        <v>26820</v>
+        <v>30800</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+81.0%</t>
+          <t>+107.8%</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2599,14 +2599,14 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>26820</v>
+        <v>30800</v>
       </c>
       <c r="K42" t="n">
-        <v>-8580</v>
+        <v>-47400</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-412.6%</t>
+          <t>-165.0%</t>
         </is>
       </c>
     </row>
@@ -2618,47 +2618,47 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>郑理</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="D43" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>8.2%</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>+32.5%</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>6600</v>
+      </c>
+      <c r="K43" t="n">
         <v>4980</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>5.0%</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-55.7%</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-100.0%</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>4980</v>
-      </c>
-      <c r="K43" t="n">
-        <v>-7709</v>
-      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-164.6%</t>
+          <t>+32.5%</t>
         </is>
       </c>
     </row>
@@ -2670,47 +2670,47 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>郑理</t>
+          <t>关万辉</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>80000</v>
+        <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>6600</v>
+        <v>23460</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-59.5%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-92.0%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>6600</v>
+        <v>21460</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>32985</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-34.9%</t>
         </is>
       </c>
     </row>
@@ -2722,47 +2722,47 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>关万辉</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="D45" t="n">
-        <v>15500</v>
+        <v>16920</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>+50.5%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-92.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>13500</v>
+        <v>16920</v>
       </c>
       <c r="K45" t="n">
-        <v>32985</v>
+        <v>-7709</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-59.1%</t>
+          <t>-319.5%</t>
         </is>
       </c>
     </row>
@@ -2774,47 +2774,47 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>刘士明</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>170000</v>
+        <v>150000</v>
       </c>
       <c r="D46" t="n">
-        <v>18960</v>
+        <v>48478</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+280.7%</t>
+          <t>+111.3%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3700</v>
+        <v>4980</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>+9.3%</t>
+          <t>-50.2%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>15260</v>
+        <v>43498</v>
       </c>
       <c r="K46" t="n">
-        <v>1594</v>
+        <v>12940</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+857.3%</t>
+          <t>+236.2%</t>
         </is>
       </c>
     </row>
@@ -2826,47 +2826,47 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>刘士明</t>
+          <t>肖伟</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>150000</v>
+        <v>170000</v>
       </c>
       <c r="D47" t="n">
-        <v>25958</v>
+        <v>66740</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+30.1%</t>
+          <t>+570.1%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>4980</v>
+        <v>3700</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+9.3%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>20978</v>
+        <v>63040</v>
       </c>
       <c r="K47" t="n">
-        <v>19960</v>
+        <v>6574</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+5.1%</t>
+          <t>+858.9%</t>
         </is>
       </c>
     </row>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -486,11 +486,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>张天昂</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -515,18 +515,18 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>+81.8%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>32990</v>
+        <v>6600</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-130.3%</t>
+          <t>-100.0%</t>
         </is>
       </c>
     </row>
@@ -538,47 +538,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>安百柠</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-82.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>151.5%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>+81.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-3400</v>
       </c>
       <c r="K3" t="n">
-        <v>-10900</v>
+        <v>32990</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-110.3%</t>
         </is>
       </c>
     </row>
@@ -590,23 +590,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>张天昂</t>
+          <t>李天阳</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>100000</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -619,18 +619,18 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="K4" t="n">
-        <v>6600</v>
+        <v>22800</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-71.1%</t>
         </is>
       </c>
     </row>
@@ -642,23 +642,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>安百柠</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>2800</v>
+        <v>8580</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-86.9%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -675,14 +675,14 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2800</v>
+        <v>8580</v>
       </c>
       <c r="K5" t="n">
-        <v>21220</v>
+        <v>-10900</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-86.8%</t>
+          <t>-178.7%</t>
         </is>
       </c>
     </row>
@@ -694,23 +694,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>李天阳</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="D6" t="n">
-        <v>6600</v>
+        <v>18300</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>+33.6%</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -723,18 +723,18 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6600</v>
+        <v>18300</v>
       </c>
       <c r="K6" t="n">
-        <v>22800</v>
+        <v>-10400</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-276.0%</t>
         </is>
       </c>
     </row>
@@ -753,16 +753,16 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>8398</v>
+        <v>14698</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-61.7%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -779,14 +779,14 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8398</v>
+        <v>14698</v>
       </c>
       <c r="K7" t="n">
         <v>20800</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-59.6%</t>
+          <t>-29.3%</t>
         </is>
       </c>
     </row>
@@ -798,23 +798,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>250000</v>
+        <v>180000</v>
       </c>
       <c r="D8" t="n">
-        <v>18300</v>
+        <v>27900</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+33.6%</t>
+          <t>+171.4%</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -831,14 +831,14 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18300</v>
+        <v>27900</v>
       </c>
       <c r="K8" t="n">
-        <v>-10400</v>
+        <v>8630</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-276.0%</t>
+          <t>+223.3%</t>
         </is>
       </c>
     </row>
@@ -850,23 +850,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>180000</v>
+        <v>100000</v>
       </c>
       <c r="D9" t="n">
-        <v>26400</v>
+        <v>22600</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+156.8%</t>
+          <t>+5.5%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -883,14 +883,14 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>26400</v>
+        <v>22600</v>
       </c>
       <c r="K9" t="n">
-        <v>8630</v>
+        <v>21220</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+205.9%</t>
+          <t>+6.5%</t>
         </is>
       </c>
     </row>
@@ -1065,16 +1065,16 @@
         <v>100000</v>
       </c>
       <c r="D13" t="n">
-        <v>61280</v>
+        <v>67880</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+828.5%</t>
+          <t>+928.5%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1091,14 +1091,14 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>61280</v>
+        <v>67880</v>
       </c>
       <c r="K13" t="n">
         <v>-3400</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-1902.4%</t>
+          <t>-2096.5%</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>58820</v>
+        <v>59320</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-41.7%</t>
+          <t>-41.2%</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1143,14 +1143,14 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4717</v>
+        <v>5217</v>
       </c>
       <c r="K14" t="n">
         <v>48071.34</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-90.2%</t>
+          <t>-89.1%</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3700</v>
+        <v>33500</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1243,18 +1243,18 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-85.1%</t>
+          <t>+35.1%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>-3700</v>
+        <v>-33500</v>
       </c>
       <c r="K16" t="n">
-        <v>39780</v>
+        <v>71180</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-109.3%</t>
+          <t>-147.1%</t>
         </is>
       </c>
     </row>
@@ -1266,47 +1266,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>唐歌</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="D17" t="n">
-        <v>20909.9</v>
+        <v>15920</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>9168</v>
+        <v>3386.66</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-85.3%</t>
+          <t>-87.7%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>11741.9</v>
+        <v>12533.34</v>
       </c>
       <c r="K17" t="n">
-        <v>17081.69</v>
+        <v>26757.72</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-53.2%</t>
         </is>
       </c>
     </row>
@@ -1318,47 +1318,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>唐歌</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="D18" t="n">
-        <v>15920</v>
+        <v>29689.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-62.7%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3386.66</v>
+        <v>9168</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-87.7%</t>
+          <t>-85.3%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>12533.34</v>
+        <v>20521.9</v>
       </c>
       <c r="K18" t="n">
-        <v>26757.72</v>
+        <v>17081.69</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-53.2%</t>
+          <t>+20.1%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-42.9%</t>
+          <t>-55.6%</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1666,11 +1666,11 @@
         <v>14920</v>
       </c>
       <c r="K24" t="n">
-        <v>19126.26</v>
+        <v>29106.26</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-48.7%</t>
         </is>
       </c>
     </row>
@@ -1682,47 +1682,47 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>黄梦妹</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>160000</v>
+        <v>100000</v>
       </c>
       <c r="D25" t="n">
-        <v>23880</v>
+        <v>15920</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>+41.1%</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>6750</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-63.2%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>17130</v>
+        <v>15920</v>
       </c>
       <c r="K25" t="n">
-        <v>19833.67</v>
+        <v>6299</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>+152.7%</t>
         </is>
       </c>
     </row>
@@ -1734,23 +1734,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>黄梦妹</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>100000</v>
+        <v>130000</v>
       </c>
       <c r="D26" t="n">
-        <v>15920</v>
+        <v>28180</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+41.1%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1767,14 +1767,14 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>15920</v>
+        <v>28180</v>
       </c>
       <c r="K26" t="n">
-        <v>6299</v>
+        <v>36198</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+152.7%</t>
+          <t>-22.2%</t>
         </is>
       </c>
     </row>
@@ -1786,47 +1786,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="D27" t="n">
-        <v>21580</v>
+        <v>39440</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-46.3%</t>
+          <t>+3.4%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>11730</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>21580</v>
+        <v>27710</v>
       </c>
       <c r="K27" t="n">
-        <v>36198</v>
+        <v>19833.67</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-40.4%</t>
+          <t>+39.7%</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+422.0%</t>
+          <t>+421.6%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1874,11 +1874,11 @@
         <v>69122</v>
       </c>
       <c r="K28" t="n">
-        <v>13318</v>
+        <v>13327.9</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+419.0%</t>
+          <t>+418.6%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+131.7%</t>
+          <t>+131.4%</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2238,11 +2238,11 @@
         <v>13920</v>
       </c>
       <c r="K35" t="n">
-        <v>401</v>
+        <v>410.8999999999996</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+3371.3%</t>
+          <t>+3287.7%</t>
         </is>
       </c>
     </row>
@@ -2313,16 +2313,16 @@
         <v>80000</v>
       </c>
       <c r="D37" t="n">
-        <v>15920</v>
+        <v>22520</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+110.1%</t>
+          <t>+197.3%</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2339,14 +2339,14 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>15920</v>
+        <v>22520</v>
       </c>
       <c r="K37" t="n">
         <v>7576</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+110.1%</t>
+          <t>+197.3%</t>
         </is>
       </c>
     </row>
@@ -2462,47 +2462,47 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="D40" t="n">
-        <v>34180</v>
+        <v>49570</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-43.8%</t>
+          <t>-53.4%</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>29800</v>
+        <v>7200</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>+358.5%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>4380</v>
+        <v>42370</v>
       </c>
       <c r="K40" t="n">
-        <v>54320</v>
+        <v>97840</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-56.7%</t>
         </is>
       </c>
     </row>
@@ -2514,47 +2514,47 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="D41" t="n">
-        <v>49570</v>
+        <v>49000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-53.4%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>7200</v>
+        <v>29800</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>+358.5%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>42370</v>
+        <v>19200</v>
       </c>
       <c r="K41" t="n">
-        <v>97840</v>
+        <v>54320</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-56.7%</t>
+          <t>-64.7%</t>
         </is>
       </c>
     </row>
@@ -2625,16 +2625,16 @@
         <v>80000</v>
       </c>
       <c r="D43" t="n">
-        <v>6600</v>
+        <v>10580</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+32.5%</t>
+          <t>+112.4%</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2651,14 +2651,14 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>6600</v>
+        <v>10580</v>
       </c>
       <c r="K43" t="n">
         <v>4980</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+32.5%</t>
+          <t>+112.4%</t>
         </is>
       </c>
     </row>
@@ -2706,11 +2706,11 @@
         <v>21460</v>
       </c>
       <c r="K44" t="n">
-        <v>32985</v>
+        <v>32994.9</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-35.0%</t>
         </is>
       </c>
     </row>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -1175,19 +1175,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>刘学锟</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>180000</v>
+        <v>30000</v>
       </c>
       <c r="D23" t="n">
-        <v>47700</v>
+        <v>7960</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1203,29 +1203,29 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>47700</v>
+        <v>7960</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>100000</v>
+        <v>180000</v>
       </c>
       <c r="D24" t="n">
-        <v>24880</v>
+        <v>47700</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,165 +1237,165 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>24880</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>160000</v>
+        <v>100000</v>
       </c>
       <c r="D25" t="n">
-        <v>39440</v>
+        <v>24880</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>11730</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>27710</v>
+        <v>24880</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>200000</v>
+        <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>49000</v>
+        <v>39440</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>29800</v>
+        <v>11730</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>19200</v>
+        <v>27710</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>200000</v>
       </c>
       <c r="D27" t="n">
-        <v>48260</v>
+        <v>49000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>18774</v>
+        <v>29800</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>29486</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>130000</v>
+        <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>28180</v>
+        <v>48260</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>18774</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>28180</v>
+        <v>29486</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>丁蕾</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>300000</v>
+        <v>130000</v>
       </c>
       <c r="D29" t="n">
-        <v>61800</v>
+        <v>28180</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,177 +1407,177 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>61800</v>
+        <v>28180</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>丁蕾</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="D30" t="n">
-        <v>49570</v>
+        <v>61800</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>41370</v>
+        <v>61800</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>黄梦妹</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="D31" t="n">
-        <v>15920</v>
+        <v>49570</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>15920</v>
+        <v>41370</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>关万辉</t>
+          <t>黄梦妹</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="D32" t="n">
-        <v>23460</v>
+        <v>15920</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>21460</v>
+        <v>15920</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>闫文奇</t>
+          <t>关万辉</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>80000</v>
+        <v>150000</v>
       </c>
       <c r="D33" t="n">
-        <v>11940</v>
+        <v>23460</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4980</v>
+        <v>2000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6960</v>
+        <v>21460</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>张露</t>
+          <t>闫文奇</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>30000</v>
+        <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>3980</v>
+        <v>11940</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>17700</v>
+        <v>4980</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>444.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>-13720</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="35">
@@ -1588,200 +1588,200 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>郑美琦</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>150000</v>
+        <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>19900</v>
+        <v>19300</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>9960</v>
+        <v>49920</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>258.7%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>9940</v>
+        <v>-30620</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>郑理</t>
+          <t>张露</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="D36" t="n">
-        <v>10580</v>
+        <v>3980</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>17700</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>444.7%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10580</v>
+        <v>-13720</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>冯岚</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="D37" t="n">
-        <v>14698</v>
+        <v>19900</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>14698</v>
+        <v>9940</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>郑理</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="D38" t="n">
-        <v>17520</v>
+        <v>10580</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>8580</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>8940</v>
+        <v>10580</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>冯岚</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>300000</v>
+        <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>33669.9</v>
+        <v>14698</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>9168</v>
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>24501.9</v>
+        <v>14698</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>李洋洋</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>40000</v>
+        <v>150000</v>
       </c>
       <c r="D40" t="n">
-        <v>3980</v>
+        <v>17520</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>8580</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3980</v>
+        <v>8940</v>
       </c>
     </row>
     <row r="41">
@@ -1792,56 +1792,56 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>闫立东</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>33669.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>9168</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>24501.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>何媛媛</t>
+          <t>李洋洋</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>150000</v>
+        <v>40000</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>33500</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1849,29 +1849,29 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-33500</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>刘学琨</t>
+          <t>闫丽东</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>30000</v>
+        <v>200000</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,22 +1883,22 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>郑美琪</t>
+          <t>何媛媛</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>130000</v>
+        <v>150000</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>33500</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>-33500</v>
       </c>
     </row>
     <row r="45">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周紫烟</t>
+          <t>周紫姻</t>
         </is>
       </c>
       <c r="C45" t="n">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -461,69 +461,69 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>王蓉</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>80000</v>
+        <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>7768</v>
+        <v>33669.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>9168</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>7768</v>
+        <v>24501.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>闫丽东</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>70000</v>
+        <v>200000</v>
       </c>
       <c r="D3" t="n">
-        <v>5874</v>
+        <v>1500</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>894</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="4">
@@ -563,27 +563,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>何媛媛</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>18800</v>
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>33500</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -591,29 +591,29 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>18800</v>
+        <v>-33500</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>安百柠</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="D6" t="n">
-        <v>8580</v>
+        <v>40780</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,29 +625,29 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8580</v>
+        <v>40780</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>刘学锟</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100000</v>
+        <v>30000</v>
       </c>
       <c r="D7" t="n">
-        <v>67880</v>
+        <v>7960</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,109 +659,109 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>67880</v>
+        <v>7960</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>龙少海</t>
+          <t>李洋洋</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>110000</v>
+        <v>40000</v>
       </c>
       <c r="D8" t="n">
-        <v>66000</v>
+        <v>3980</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>24800</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>41200</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>李天阳</t>
+          <t>张露</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>100000</v>
+        <v>30000</v>
       </c>
       <c r="D9" t="n">
-        <v>6600</v>
+        <v>3980</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>17700</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>444.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6600</v>
+        <v>-13720</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100000</v>
+        <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>54900</v>
+        <v>65540</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>54900</v>
+        <v>65142</v>
       </c>
     </row>
     <row r="11">
@@ -772,52 +772,52 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>黄梦妹</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>130000</v>
+        <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>65540</v>
+        <v>15920</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>65142</v>
+        <v>15920</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>高铭瑞</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>100000</v>
+        <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>45800</v>
+        <v>28180</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,279 +829,279 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>45800</v>
+        <v>28180</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>姜人荷</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>53220</v>
+        <v>19900</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>53220</v>
+        <v>9940</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>梁志超</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>300000</v>
+        <v>160000</v>
       </c>
       <c r="D14" t="n">
-        <v>127894</v>
+        <v>39440</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>66228</v>
+        <v>11730</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>61666</v>
+        <v>27710</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>樊帆</t>
+          <t>郑美琦</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80000</v>
+        <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>32568</v>
+        <v>19300</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3156.67</v>
+        <v>49920</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>258.7%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>29411.33</v>
+        <v>-30620</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>段继宇</t>
+          <t>梁志超</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>80000</v>
+        <v>300000</v>
       </c>
       <c r="D16" t="n">
-        <v>3788</v>
+        <v>127894</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>66228</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3788</v>
+        <v>61666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>丁蕾</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>170000</v>
+        <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>66740</v>
+        <v>61800</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>7700</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>59040</v>
+        <v>61800</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>周紫姻</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>80000</v>
+        <v>50000</v>
       </c>
       <c r="D18" t="n">
-        <v>27860</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2596.6</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>25263.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>刘士明</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>48478</v>
+        <v>27860</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4980</v>
+        <v>2596.6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>43498</v>
+        <v>25263.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>段继宇</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="D20" t="n">
-        <v>6600</v>
+        <v>3788</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>151.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-3400</v>
+        <v>3788</v>
       </c>
     </row>
     <row r="21">
@@ -1112,120 +1112,120 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>樊帆</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>80000</v>
       </c>
       <c r="D21" t="n">
-        <v>22520</v>
+        <v>32568</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3156.67</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>22520</v>
+        <v>29411.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>150000</v>
       </c>
       <c r="D22" t="n">
-        <v>40780</v>
+        <v>17520</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>8580</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>40780</v>
+        <v>8940</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>刘学锟</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>30000</v>
+        <v>70000</v>
       </c>
       <c r="D23" t="n">
-        <v>7960</v>
+        <v>5874</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>7960</v>
+        <v>894</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>王蓉</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>180000</v>
+        <v>80000</v>
       </c>
       <c r="D24" t="n">
-        <v>47700</v>
+        <v>7768</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,29 +1237,29 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>47700</v>
+        <v>7768</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="D25" t="n">
-        <v>24880</v>
+        <v>22520</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1271,41 +1271,41 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>24880</v>
+        <v>22520</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>闫文奇</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>160000</v>
+        <v>80000</v>
       </c>
       <c r="D26" t="n">
-        <v>39440</v>
+        <v>11940</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>11730</v>
+        <v>4980</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>27710</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="27">
@@ -1316,86 +1316,86 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>49000</v>
+        <v>49570</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>29800</v>
+        <v>8200</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>19200</v>
+        <v>41370</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>48260</v>
+        <v>49000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>18774</v>
+        <v>29800</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>29486</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>高铭瑞</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>130000</v>
+        <v>100000</v>
       </c>
       <c r="D29" t="n">
-        <v>28180</v>
+        <v>45800</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,29 +1407,29 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>28180</v>
+        <v>45800</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>丁蕾</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="D30" t="n">
-        <v>61800</v>
+        <v>24880</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,75 +1441,75 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>61800</v>
+        <v>24880</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>关万辉</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="D31" t="n">
-        <v>49570</v>
+        <v>23460</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>8200</v>
+        <v>2000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>41370</v>
+        <v>21460</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>黄梦妹</t>
+          <t>刘士明</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="D32" t="n">
-        <v>15920</v>
+        <v>48478</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>15920</v>
+        <v>43498</v>
       </c>
     </row>
     <row r="33">
@@ -1520,188 +1520,188 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>关万辉</t>
+          <t>肖伟</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>150000</v>
+        <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>23460</v>
+        <v>66740</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>21460</v>
+        <v>59040</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>闫文奇</t>
+          <t>郑理</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>11940</v>
+        <v>10580</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>6960</v>
+        <v>10580</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>郑美琦</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>130000</v>
+        <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>19300</v>
+        <v>48260</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>49920</v>
+        <v>18774</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>258.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-30620</v>
+        <v>29486</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>张露</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>30000</v>
+        <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>3980</v>
+        <v>6600</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>17700</v>
+        <v>10000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>444.7%</t>
+          <t>151.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>-13720</v>
+        <v>-3400</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="D37" t="n">
-        <v>19900</v>
+        <v>18800</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>9960</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>9940</v>
+        <v>18800</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>郑理</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>80000</v>
+        <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>10580</v>
+        <v>47700</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>10580</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="39">
@@ -1724,18 +1724,18 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>冯岚</t>
+          <t>李天阳</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>120000</v>
+        <v>100000</v>
       </c>
       <c r="D39" t="n">
-        <v>14698</v>
+        <v>6600</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1747,97 +1747,97 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>14698</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>姜人荷</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="D40" t="n">
-        <v>17520</v>
+        <v>53220</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>8580</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>8940</v>
+        <v>53220</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>安百柠</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>300000</v>
+        <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>33669.9</v>
+        <v>8580</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>9168</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>24501.9</v>
+        <v>8580</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>李洋洋</t>
+          <t>冯岚</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>40000</v>
+        <v>120000</v>
       </c>
       <c r="D42" t="n">
-        <v>3980</v>
+        <v>14698</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1849,29 +1849,29 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3980</v>
+        <v>14698</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>闫丽东</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="D43" t="n">
-        <v>1500</v>
+        <v>54900</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,22 +1883,22 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1500</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>何媛媛</t>
+          <t>张天昂</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>33500</v>
+        <v>0</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1917,29 +1917,29 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>-33500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周紫姻</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>67880</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>67880</v>
       </c>
     </row>
     <row r="46">
@@ -1962,30 +1962,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>张天昂</t>
+          <t>龙少海</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>41200</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -473,23 +473,23 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>33669.9</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9168</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>24501.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>200000</v>
       </c>
       <c r="D3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>200000</v>
       </c>
       <c r="D4" t="n">
-        <v>15920</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3386.66</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>12533.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>33500</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-33500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>150000</v>
       </c>
       <c r="D6" t="n">
-        <v>40780</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>30000</v>
       </c>
       <c r="D7" t="n">
-        <v>7960</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7960</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>40000</v>
       </c>
       <c r="D8" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>30000</v>
       </c>
       <c r="D9" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>17700</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>444.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-13720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -745,23 +745,23 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>65540</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>65142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>15920</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>15920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>28180</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>28180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -847,23 +847,23 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>19900</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9960</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9940</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -881,23 +881,23 @@
         <v>160000</v>
       </c>
       <c r="D14" t="n">
-        <v>39440</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>11730</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>27710</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -915,23 +915,23 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>19300</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>49920</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>258.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-30620</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -949,23 +949,23 @@
         <v>300000</v>
       </c>
       <c r="D16" t="n">
-        <v>127894</v>
+        <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>66228</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>61666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>61800</v>
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>61800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1051,23 +1051,23 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>27860</v>
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2596.6</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>25263.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>80000</v>
       </c>
       <c r="D20" t="n">
-        <v>3788</v>
+        <v>0</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1119,23 +1119,23 @@
         <v>80000</v>
       </c>
       <c r="D21" t="n">
-        <v>32568</v>
+        <v>0</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3156.67</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>29411.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1153,23 +1153,23 @@
         <v>150000</v>
       </c>
       <c r="D22" t="n">
-        <v>17520</v>
+        <v>0</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8580</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>8940</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1187,23 +1187,23 @@
         <v>70000</v>
       </c>
       <c r="D23" t="n">
-        <v>5874</v>
+        <v>0</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>80000</v>
       </c>
       <c r="D24" t="n">
-        <v>7768</v>
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>7768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>80000</v>
       </c>
       <c r="D25" t="n">
-        <v>22520</v>
+        <v>0</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>22520</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1289,23 +1289,23 @@
         <v>80000</v>
       </c>
       <c r="D26" t="n">
-        <v>11940</v>
+        <v>0</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6960</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1323,23 +1323,23 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>49570</v>
+        <v>0</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>41370</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1357,23 +1357,23 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>49000</v>
+        <v>0</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>29800</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>19200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>100000</v>
       </c>
       <c r="D29" t="n">
-        <v>45800</v>
+        <v>0</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>45800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>100000</v>
       </c>
       <c r="D30" t="n">
-        <v>24880</v>
+        <v>0</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>24880</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1459,23 +1459,23 @@
         <v>150000</v>
       </c>
       <c r="D31" t="n">
-        <v>23460</v>
+        <v>0</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>21460</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1493,23 +1493,23 @@
         <v>150000</v>
       </c>
       <c r="D32" t="n">
-        <v>48478</v>
+        <v>0</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>43498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1527,23 +1527,23 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>66740</v>
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>7700</v>
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>59040</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>10580</v>
+        <v>0</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>10580</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1595,23 +1595,23 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>48260</v>
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>18774</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29486</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1629,23 +1629,23 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>151.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>-3400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>250000</v>
       </c>
       <c r="D37" t="n">
-        <v>18800</v>
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>18800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1697,11 +1697,11 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>47700</v>
+        <v>0</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>47700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1731,11 +1731,11 @@
         <v>100000</v>
       </c>
       <c r="D39" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1765,11 +1765,11 @@
         <v>120000</v>
       </c>
       <c r="D40" t="n">
-        <v>53220</v>
+        <v>0</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>53220</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>8580</v>
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>8580</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>120000</v>
       </c>
       <c r="D42" t="n">
-        <v>14698</v>
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>14698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>100000</v>
       </c>
       <c r="D43" t="n">
-        <v>54900</v>
+        <v>0</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>54900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1935,11 +1935,11 @@
         <v>100000</v>
       </c>
       <c r="D45" t="n">
-        <v>67880</v>
+        <v>0</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>67880</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1969,23 +1969,23 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>24800</v>
+        <v>0</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>41200</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -473,23 +473,23 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>41629.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>14148</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>27481.9</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>200000</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3386</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>225.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-1886</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>200000</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>27860</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3386.66</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>24473.34</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>33500</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>841.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-29520</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>150000</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>44760</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>19960</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>30000</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>7960</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>7960</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>40000</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>30000</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>17700</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>444.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-13720</v>
       </c>
     </row>
     <row r="10">
@@ -745,23 +745,23 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>89320</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>5378</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>83942</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>15920</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>15920</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>32160</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>32160</v>
       </c>
     </row>
     <row r="13">
@@ -847,23 +847,23 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>19900</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>9940</v>
       </c>
     </row>
     <row r="14">
@@ -881,23 +881,23 @@
         <v>160000</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>39440</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>11730</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>27710</v>
       </c>
     </row>
     <row r="15">
@@ -915,23 +915,23 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>19300</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>49920</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>258.7%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-30620</v>
       </c>
     </row>
     <row r="16">
@@ -949,23 +949,23 @@
         <v>300000</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>127894</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>66228</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>61666</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>105400</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>105400</v>
       </c>
     </row>
     <row r="18">
@@ -1051,23 +1051,23 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>27860</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2596.6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>25263.4</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>80000</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>7768</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>7768</v>
       </c>
     </row>
     <row r="21">
@@ -1119,23 +1119,23 @@
         <v>80000</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>36548</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3156.67</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>33391.33</v>
       </c>
     </row>
     <row r="22">
@@ -1153,23 +1153,23 @@
         <v>150000</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>8580</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>12920</v>
       </c>
     </row>
     <row r="23">
@@ -1187,23 +1187,23 @@
         <v>70000</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>9854</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>4874</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>80000</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>7768</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>7768</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>80000</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>26500</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="26">
@@ -1289,23 +1289,23 @@
         <v>80000</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>19900</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>14920</v>
       </c>
     </row>
     <row r="27">
@@ -1323,23 +1323,23 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>55764</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>47564</v>
       </c>
     </row>
     <row r="28">
@@ -1357,23 +1357,23 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>52980</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>29800</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>23180</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>100000</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>49780</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>49780</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>100000</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>24880</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>24880</v>
       </c>
     </row>
     <row r="31">
@@ -1459,23 +1459,23 @@
         <v>150000</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>23460</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>21460</v>
       </c>
     </row>
     <row r="32">
@@ -1493,23 +1493,23 @@
         <v>150000</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>48478</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>11580</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>36898</v>
       </c>
     </row>
     <row r="33">
@@ -1527,23 +1527,23 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>66740</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>59040</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>14560</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>14560</v>
       </c>
     </row>
     <row r="35">
@@ -1595,23 +1595,23 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>48260</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>48574</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.7%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>-314</v>
       </c>
     </row>
     <row r="36">
@@ -1629,23 +1629,23 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>151.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>-3400</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>250000</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>18800</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>18800</v>
       </c>
     </row>
     <row r="38">
@@ -1697,11 +1697,11 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>48200</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>48200</v>
       </c>
     </row>
     <row r="39">
@@ -1731,11 +1731,11 @@
         <v>100000</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="40">
@@ -1765,11 +1765,11 @@
         <v>120000</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>55710</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>55710</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>8580</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>8580</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>120000</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>21298</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>21298</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>100000</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>54900</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="44">
@@ -1935,11 +1935,11 @@
         <v>100000</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>76700</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>76700</v>
       </c>
     </row>
     <row r="46">
@@ -1969,23 +1969,23 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>41200</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -473,11 +473,11 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>41629.9</v>
+        <v>49589.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>27481.9</v>
+        <v>35441.9</v>
       </c>
     </row>
     <row r="3">
@@ -549,15 +549,15 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3386.66</v>
+        <v>8366.66</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>24473.34</v>
+        <v>19493.34</v>
       </c>
     </row>
     <row r="5">
@@ -949,11 +949,11 @@
         <v>300000</v>
       </c>
       <c r="D16" t="n">
-        <v>127894</v>
+        <v>132882</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>61666</v>
+        <v>66654</v>
       </c>
     </row>
     <row r="17">
@@ -1153,11 +1153,11 @@
         <v>150000</v>
       </c>
       <c r="D22" t="n">
-        <v>21500</v>
+        <v>29080</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1165,11 +1165,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>12920</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>70000</v>
       </c>
       <c r="D23" t="n">
-        <v>9854</v>
+        <v>17814</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4874</v>
+        <v>12834</v>
       </c>
     </row>
     <row r="24">
@@ -1357,11 +1357,11 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>52980</v>
+        <v>56960</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>23180</v>
+        <v>27160</v>
       </c>
     </row>
     <row r="29">
@@ -1459,11 +1459,11 @@
         <v>150000</v>
       </c>
       <c r="D31" t="n">
-        <v>23460</v>
+        <v>33460</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>21460</v>
+        <v>31460</v>
       </c>
     </row>
     <row r="32">
@@ -1527,11 +1527,11 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>66740</v>
+        <v>79940</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>59040</v>
+        <v>72240</v>
       </c>
     </row>
     <row r="34">
@@ -1629,11 +1629,11 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>6600</v>
+        <v>36400</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>151.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>-3400</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="37">
@@ -1697,19 +1697,19 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>48200</v>
+        <v>73000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -1731,23 +1731,23 @@
         <v>100000</v>
       </c>
       <c r="D39" t="n">
-        <v>6600</v>
+        <v>36400</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>4950</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>6600</v>
+        <v>31450</v>
       </c>
     </row>
     <row r="40">
@@ -1765,11 +1765,11 @@
         <v>120000</v>
       </c>
       <c r="D40" t="n">
-        <v>55710</v>
+        <v>76108</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>55710</v>
+        <v>76108</v>
       </c>
     </row>
     <row r="41">
@@ -1867,11 +1867,11 @@
         <v>100000</v>
       </c>
       <c r="D43" t="n">
-        <v>54900</v>
+        <v>66900</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>54900</v>
+        <v>66900</v>
       </c>
     </row>
     <row r="44">
@@ -1935,11 +1935,11 @@
         <v>100000</v>
       </c>
       <c r="D45" t="n">
-        <v>76700</v>
+        <v>87680</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>76700</v>
+        <v>87680</v>
       </c>
     </row>
     <row r="46">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>3980</v>
+        <v>7960</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>841.7%</t>
+          <t>420.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-29520</v>
+        <v>-25540</v>
       </c>
     </row>
     <row r="6">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>15920</v>
+        <v>19900</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>15920</v>
+        <v>19900</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>32160</v>
+        <v>38760</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>32160</v>
+        <v>38760</v>
       </c>
     </row>
     <row r="13">
@@ -915,11 +915,11 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>19300</v>
+        <v>40720</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>258.7%</t>
+          <t>122.6%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-30620</v>
+        <v>-9200</v>
       </c>
     </row>
     <row r="16">
@@ -1629,11 +1629,11 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>36400</v>
+        <v>46400</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>26400</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="37">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -473,11 +473,11 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>49589.9</v>
+        <v>105789.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>35441.9</v>
+        <v>91641.89999999999</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>200000</v>
       </c>
       <c r="D3" t="n">
-        <v>1500</v>
+        <v>8100</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>225.7%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-1886</v>
+        <v>4714</v>
       </c>
     </row>
     <row r="4">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>7960</v>
+        <v>13620</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>420.9%</t>
+          <t>246.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-25540</v>
+        <v>-19880</v>
       </c>
     </row>
     <row r="6">
@@ -617,15 +617,15 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>24800</v>
+        <v>28983</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>19960</v>
+        <v>15777</v>
       </c>
     </row>
     <row r="7">
@@ -677,19 +677,19 @@
         <v>40000</v>
       </c>
       <c r="D8" t="n">
-        <v>3980</v>
+        <v>23980</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -711,11 +711,11 @@
         <v>30000</v>
       </c>
       <c r="D9" t="n">
-        <v>3980</v>
+        <v>7960</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>444.7%</t>
+          <t>222.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-13720</v>
+        <v>-9740</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>89320</v>
+        <v>95290</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>83942</v>
+        <v>89912</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>19900</v>
+        <v>23880</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19900</v>
+        <v>23880</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>38760</v>
+        <v>42740</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>38760</v>
+        <v>42740</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>19900</v>
+        <v>31840</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9940</v>
+        <v>21880</v>
       </c>
     </row>
     <row r="14">
@@ -881,23 +881,23 @@
         <v>160000</v>
       </c>
       <c r="D14" t="n">
-        <v>39440</v>
+        <v>49080</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>11730</v>
+        <v>16710</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>27710</v>
+        <v>32370</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>40720</v>
+        <v>59520</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>122.6%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-9200</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>300000</v>
       </c>
       <c r="D16" t="n">
-        <v>132882</v>
+        <v>134776</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>66654</v>
+        <v>68548</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>105400</v>
+        <v>253388.01</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>105400</v>
+        <v>253388.01</v>
       </c>
     </row>
     <row r="18">
@@ -1093,15 +1093,15 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4150</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>7768</v>
+        <v>3618</v>
       </c>
     </row>
     <row r="21">
@@ -1153,23 +1153,23 @@
         <v>150000</v>
       </c>
       <c r="D22" t="n">
-        <v>29080</v>
+        <v>29580</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8580</v>
+        <v>12179</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>20500</v>
+        <v>17401</v>
       </c>
     </row>
     <row r="23">
@@ -1323,11 +1323,11 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>55764</v>
+        <v>91164</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>47564</v>
+        <v>82964</v>
       </c>
     </row>
     <row r="28">
@@ -1425,11 +1425,11 @@
         <v>100000</v>
       </c>
       <c r="D30" t="n">
-        <v>24880</v>
+        <v>32840</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>24880</v>
+        <v>32840</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>150000</v>
       </c>
       <c r="D31" t="n">
-        <v>33460</v>
+        <v>51420</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>31460</v>
+        <v>49420</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>150000</v>
       </c>
       <c r="D32" t="n">
-        <v>48478</v>
+        <v>52458</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>36898</v>
+        <v>40878</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>79940</v>
+        <v>100840</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>72240</v>
+        <v>93140</v>
       </c>
     </row>
     <row r="34">
@@ -1561,23 +1561,23 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>14560</v>
+        <v>26500</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>14560</v>
+        <v>21520</v>
       </c>
     </row>
     <row r="35">
@@ -1697,11 +1697,11 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>73000</v>
+        <v>74500</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1709,11 +1709,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>48200</v>
+        <v>49700</v>
       </c>
     </row>
     <row r="39">
@@ -1731,11 +1731,11 @@
         <v>100000</v>
       </c>
       <c r="D39" t="n">
-        <v>36400</v>
+        <v>46400</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1743,11 +1743,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>31450</v>
+        <v>41450</v>
       </c>
     </row>
     <row r="40">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>8580</v>
+        <v>33380</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>8580</v>
+        <v>33380</v>
       </c>
     </row>
     <row r="42">
@@ -1875,15 +1875,15 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>66900</v>
+        <v>62900</v>
       </c>
     </row>
     <row r="44">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -473,11 +473,11 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>105789.9</v>
+        <v>74389.89999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>91641.89999999999</v>
+        <v>60241.89999999999</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>200000</v>
       </c>
       <c r="D3" t="n">
-        <v>8100</v>
+        <v>1500</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>225.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4714</v>
+        <v>-1886</v>
       </c>
     </row>
     <row r="4">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>13620</v>
+        <v>7960</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>246.0%</t>
+          <t>420.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-19880</v>
+        <v>-25540</v>
       </c>
     </row>
     <row r="6">
@@ -617,15 +617,15 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>28983</v>
+        <v>24800</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>15777</v>
+        <v>19960</v>
       </c>
     </row>
     <row r="7">
@@ -685,15 +685,15 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3980</v>
+        <v>23980</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>30000</v>
       </c>
       <c r="D9" t="n">
-        <v>7960</v>
+        <v>3980</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>222.4%</t>
+          <t>444.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-9740</v>
+        <v>-13720</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>95290</v>
+        <v>87330</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>89912</v>
+        <v>81952</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>23880</v>
+        <v>19900</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>23880</v>
+        <v>19900</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>42740</v>
+        <v>38760</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>42740</v>
+        <v>38760</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>31840</v>
+        <v>23880</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>21880</v>
+        <v>13920</v>
       </c>
     </row>
     <row r="14">
@@ -881,23 +881,23 @@
         <v>160000</v>
       </c>
       <c r="D14" t="n">
-        <v>49080</v>
+        <v>41120</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>16710</v>
+        <v>11730</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>32370</v>
+        <v>29390</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>59520</v>
+        <v>40720</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>122.6%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>9600</v>
+        <v>-9200</v>
       </c>
     </row>
     <row r="16">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>253388.01</v>
+        <v>186988</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>253388.01</v>
+        <v>186988</v>
       </c>
     </row>
     <row r="18">
@@ -1093,15 +1093,15 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4150</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3618</v>
+        <v>7768</v>
       </c>
     </row>
     <row r="21">
@@ -1161,15 +1161,15 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12179</v>
+        <v>8580</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>17401</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="23">
@@ -1323,11 +1323,11 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>91164</v>
+        <v>62364</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>82964</v>
+        <v>54164</v>
       </c>
     </row>
     <row r="28">
@@ -1425,11 +1425,11 @@
         <v>100000</v>
       </c>
       <c r="D30" t="n">
-        <v>32840</v>
+        <v>24880</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>32840</v>
+        <v>24880</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>150000</v>
       </c>
       <c r="D31" t="n">
-        <v>51420</v>
+        <v>33460</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>49420</v>
+        <v>31460</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>150000</v>
       </c>
       <c r="D32" t="n">
-        <v>52458</v>
+        <v>48478</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>40878</v>
+        <v>36898</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>100840</v>
+        <v>83920</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>93140</v>
+        <v>76220</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>26500</v>
+        <v>14560</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21520</v>
+        <v>9580</v>
       </c>
     </row>
     <row r="35">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>33380</v>
+        <v>8580</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>33380</v>
+        <v>8580</v>
       </c>
     </row>
     <row r="42">
@@ -1875,15 +1875,15 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>62900</v>
+        <v>66900</v>
       </c>
     </row>
     <row r="44">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -473,11 +473,11 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>74389.89999999999</v>
+        <v>105789.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>60241.89999999999</v>
+        <v>91641.89999999999</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>200000</v>
       </c>
       <c r="D3" t="n">
-        <v>1500</v>
+        <v>8100</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>225.7%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-1886</v>
+        <v>4714</v>
       </c>
     </row>
     <row r="4">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>7960</v>
+        <v>13620</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>420.9%</t>
+          <t>246.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-25540</v>
+        <v>-19880</v>
       </c>
     </row>
     <row r="6">
@@ -617,15 +617,15 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>24800</v>
+        <v>28983</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>19960</v>
+        <v>15777</v>
       </c>
     </row>
     <row r="7">
@@ -685,15 +685,15 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23980</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>30000</v>
       </c>
       <c r="D9" t="n">
-        <v>3980</v>
+        <v>7960</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>444.7%</t>
+          <t>222.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-13720</v>
+        <v>-9740</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>87330</v>
+        <v>95290</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>81952</v>
+        <v>89912</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>19900</v>
+        <v>23880</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19900</v>
+        <v>23880</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>38760</v>
+        <v>42740</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>38760</v>
+        <v>42740</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>23880</v>
+        <v>31840</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>13920</v>
+        <v>21880</v>
       </c>
     </row>
     <row r="14">
@@ -881,23 +881,23 @@
         <v>160000</v>
       </c>
       <c r="D14" t="n">
-        <v>41120</v>
+        <v>49080</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>11730</v>
+        <v>16710</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>29390</v>
+        <v>32370</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>40720</v>
+        <v>59520</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>122.6%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-9200</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="16">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>186988</v>
+        <v>253388.01</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>186988</v>
+        <v>253388.01</v>
       </c>
     </row>
     <row r="18">
@@ -1093,15 +1093,15 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4150</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>7768</v>
+        <v>3618</v>
       </c>
     </row>
     <row r="21">
@@ -1161,15 +1161,15 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8580</v>
+        <v>12179</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>21000</v>
+        <v>17401</v>
       </c>
     </row>
     <row r="23">
@@ -1323,11 +1323,11 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>62364</v>
+        <v>91164</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>54164</v>
+        <v>82964</v>
       </c>
     </row>
     <row r="28">
@@ -1425,11 +1425,11 @@
         <v>100000</v>
       </c>
       <c r="D30" t="n">
-        <v>24880</v>
+        <v>32840</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>24880</v>
+        <v>32840</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>150000</v>
       </c>
       <c r="D31" t="n">
-        <v>33460</v>
+        <v>51420</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>31460</v>
+        <v>49420</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>150000</v>
       </c>
       <c r="D32" t="n">
-        <v>48478</v>
+        <v>52458</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>36898</v>
+        <v>40878</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>83920</v>
+        <v>100840</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>76220</v>
+        <v>93140</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>14560</v>
+        <v>26500</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>9580</v>
+        <v>21520</v>
       </c>
     </row>
     <row r="35">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>8580</v>
+        <v>33380</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>8580</v>
+        <v>33380</v>
       </c>
     </row>
     <row r="42">
@@ -1875,15 +1875,15 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>66900</v>
+        <v>62900</v>
       </c>
     </row>
     <row r="44">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -473,23 +473,23 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>105789.9</v>
+        <v>112389.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>14148</v>
+        <v>19148</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>91641.89999999999</v>
+        <v>93241.89999999999</v>
       </c>
     </row>
     <row r="3">
@@ -745,11 +745,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>95290</v>
+        <v>120090</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>89912</v>
+        <v>114712</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>23880</v>
+        <v>27860</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>23880</v>
+        <v>27860</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>42740</v>
+        <v>46720</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>42740</v>
+        <v>46720</v>
       </c>
     </row>
     <row r="13">
@@ -915,11 +915,11 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>59520</v>
+        <v>74340</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>9600</v>
+        <v>24420</v>
       </c>
     </row>
     <row r="16">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>253388.01</v>
+        <v>259328.01</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>253388.01</v>
+        <v>259328.01</v>
       </c>
     </row>
     <row r="18">
@@ -1187,11 +1187,11 @@
         <v>70000</v>
       </c>
       <c r="D23" t="n">
-        <v>17814</v>
+        <v>19708</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>12834</v>
+        <v>14728</v>
       </c>
     </row>
     <row r="24">
@@ -1229,15 +1229,15 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>7768</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="25">
@@ -1323,11 +1323,11 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>91164</v>
+        <v>93144</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>82964</v>
+        <v>84944</v>
       </c>
     </row>
     <row r="28">
@@ -1493,11 +1493,11 @@
         <v>150000</v>
       </c>
       <c r="D32" t="n">
-        <v>52458</v>
+        <v>56438</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>40878</v>
+        <v>44858</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>100840</v>
+        <v>104820</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>93140</v>
+        <v>97120</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>26500</v>
+        <v>30480</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21520</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>48260</v>
+        <v>81260</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>100.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-314</v>
+        <v>32686</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>46400</v>
+        <v>54320</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>36400</v>
+        <v>44320</v>
       </c>
     </row>
     <row r="37">
@@ -1697,11 +1697,11 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>74500</v>
+        <v>84500</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1709,11 +1709,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>49700</v>
+        <v>59700</v>
       </c>
     </row>
     <row r="39">
@@ -1773,15 +1773,15 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>76108</v>
+        <v>70108</v>
       </c>
     </row>
     <row r="41">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -677,11 +677,11 @@
         <v>40000</v>
       </c>
       <c r="D8" t="n">
-        <v>23980</v>
+        <v>26140</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3980</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="9">
@@ -821,15 +821,15 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>4183</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>46720</v>
+        <v>42537</v>
       </c>
     </row>
     <row r="13">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>259328.01</v>
+        <v>261308.01</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>259328.01</v>
+        <v>261308.01</v>
       </c>
     </row>
     <row r="18">
@@ -1051,11 +1051,11 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>27860</v>
+        <v>31840</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>25263.4</v>
+        <v>29243.4</v>
       </c>
     </row>
     <row r="20">
@@ -1323,23 +1323,23 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>93144</v>
+        <v>99744</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>8200</v>
+        <v>9880</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>84944</v>
+        <v>89864</v>
       </c>
     </row>
     <row r="28">
@@ -1663,11 +1663,11 @@
         <v>250000</v>
       </c>
       <c r="D37" t="n">
-        <v>18800</v>
+        <v>19300</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>18800</v>
+        <v>19300</v>
       </c>
     </row>
     <row r="38">
@@ -1697,11 +1697,11 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>84500</v>
+        <v>91100</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1709,11 +1709,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>59700</v>
+        <v>66300</v>
       </c>
     </row>
     <row r="39">
@@ -1935,11 +1935,11 @@
         <v>100000</v>
       </c>
       <c r="D45" t="n">
-        <v>87680</v>
+        <v>91468</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>87680</v>
+        <v>91468</v>
       </c>
     </row>
     <row r="46">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -473,23 +473,23 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>112389.9</v>
+        <v>128929.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>19148</v>
+        <v>23298</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>93241.89999999999</v>
+        <v>105631.9</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>200000</v>
       </c>
       <c r="D3" t="n">
-        <v>8100</v>
+        <v>38880</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4714</v>
+        <v>35494</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>200000</v>
       </c>
       <c r="D4" t="n">
-        <v>27860</v>
+        <v>35820</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -553,11 +553,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>19493.34</v>
+        <v>27453.34</v>
       </c>
     </row>
     <row r="5">
@@ -609,11 +609,11 @@
         <v>150000</v>
       </c>
       <c r="D6" t="n">
-        <v>44760</v>
+        <v>60740</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>15777</v>
+        <v>31757</v>
       </c>
     </row>
     <row r="7">
@@ -847,11 +847,11 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>31840</v>
+        <v>39800</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>21880</v>
+        <v>29840</v>
       </c>
     </row>
     <row r="14">
@@ -1051,11 +1051,11 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>31840</v>
+        <v>51740</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>29243.4</v>
+        <v>49143.4</v>
       </c>
     </row>
     <row r="20">
@@ -1153,11 +1153,11 @@
         <v>150000</v>
       </c>
       <c r="D22" t="n">
-        <v>29580</v>
+        <v>41529.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1165,11 +1165,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>17401</v>
+        <v>29350.9</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>70000</v>
       </c>
       <c r="D23" t="n">
-        <v>19708</v>
+        <v>23688</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>14728</v>
+        <v>18708</v>
       </c>
     </row>
     <row r="24">
@@ -1289,11 +1289,11 @@
         <v>80000</v>
       </c>
       <c r="D26" t="n">
-        <v>19900</v>
+        <v>27860</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>14920</v>
+        <v>22880</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>99744</v>
+        <v>107704</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>89864</v>
+        <v>97824</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>56960</v>
+        <v>60940</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>27160</v>
+        <v>31140</v>
       </c>
     </row>
     <row r="29">
@@ -1527,11 +1527,11 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>104820</v>
+        <v>108800</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>97120</v>
+        <v>101100</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>30480</v>
+        <v>26500</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>25500</v>
+        <v>21520</v>
       </c>
     </row>
     <row r="35">
@@ -1867,11 +1867,11 @@
         <v>100000</v>
       </c>
       <c r="D43" t="n">
-        <v>66900</v>
+        <v>61920</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1879,11 +1879,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>62900</v>
+        <v>57920</v>
       </c>
     </row>
     <row r="44">
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>13200</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>-13200</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>100000</v>
       </c>
       <c r="D45" t="n">
-        <v>91468</v>
+        <v>86488</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>91468</v>
+        <v>86488</v>
       </c>
     </row>
     <row r="46">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -473,23 +473,23 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>128929.9</v>
+        <v>170869.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23298</v>
+        <v>53098</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>105631.9</v>
+        <v>117771.9</v>
       </c>
     </row>
     <row r="3">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>13620</v>
+        <v>21580</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>246.0%</t>
+          <t>155.2%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-19880</v>
+        <v>-11920</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>150000</v>
       </c>
       <c r="D6" t="n">
-        <v>60740</v>
+        <v>61740</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>31757</v>
+        <v>32757</v>
       </c>
     </row>
     <row r="7">
@@ -651,15 +651,15 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7960</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="8">
@@ -745,11 +745,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>120090</v>
+        <v>183290</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>141.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>114712</v>
+        <v>177912</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>27860</v>
+        <v>31840</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>27860</v>
+        <v>31840</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>46720</v>
+        <v>66520</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>42537</v>
+        <v>62337</v>
       </c>
     </row>
     <row r="13">
@@ -915,11 +915,11 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>74340</v>
+        <v>94140</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>24420</v>
+        <v>44220</v>
       </c>
     </row>
     <row r="16">
@@ -1017,11 +1017,11 @@
         <v>50000</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="19">
@@ -1085,11 +1085,11 @@
         <v>80000</v>
       </c>
       <c r="D20" t="n">
-        <v>7768</v>
+        <v>15728</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3618</v>
+        <v>11578</v>
       </c>
     </row>
     <row r="21">
@@ -1161,15 +1161,15 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12179</v>
+        <v>15779</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>29350.9</v>
+        <v>25750.9</v>
       </c>
     </row>
     <row r="23">
@@ -1255,11 +1255,11 @@
         <v>80000</v>
       </c>
       <c r="D25" t="n">
-        <v>26500</v>
+        <v>38440</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>26500</v>
+        <v>38440</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>80000</v>
       </c>
       <c r="D26" t="n">
-        <v>27860</v>
+        <v>31840</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>22880</v>
+        <v>26860</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>107704</v>
+        <v>111684</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>97824</v>
+        <v>101804</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>60940</v>
+        <v>64920</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>31140</v>
+        <v>35120</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>100000</v>
       </c>
       <c r="D29" t="n">
-        <v>49780</v>
+        <v>64600</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>49780</v>
+        <v>64600</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>100000</v>
       </c>
       <c r="D30" t="n">
-        <v>32840</v>
+        <v>42840</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>32840</v>
+        <v>42840</v>
       </c>
     </row>
     <row r="31">
@@ -1467,15 +1467,15 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>49420</v>
+        <v>34420</v>
       </c>
     </row>
     <row r="32">
@@ -1501,15 +1501,15 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>11580</v>
+        <v>21580</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>44858</v>
+        <v>34858</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>108800</v>
+        <v>115400</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>101100</v>
+        <v>107700</v>
       </c>
     </row>
     <row r="34">
@@ -1569,15 +1569,15 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4980</v>
+        <v>11580</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21520</v>
+        <v>14920</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>81260</v>
+        <v>114260</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>32686</v>
+        <v>65686</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>54320</v>
+        <v>58280</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>44320</v>
+        <v>48280</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>250000</v>
       </c>
       <c r="D37" t="n">
-        <v>19300</v>
+        <v>20800</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>19300</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="38">
@@ -1697,11 +1697,11 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>91100</v>
+        <v>112520</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1709,11 +1709,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>66300</v>
+        <v>87720</v>
       </c>
     </row>
     <row r="39">
@@ -1969,11 +1969,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>66000</v>
+        <v>67000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1981,11 +1981,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>41200</v>
+        <v>42200</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -481,15 +481,15 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>53098</v>
+        <v>63098</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>117771.9</v>
+        <v>107771.9</v>
       </c>
     </row>
     <row r="3">
@@ -507,19 +507,19 @@
         <v>200000</v>
       </c>
       <c r="D3" t="n">
-        <v>38880</v>
+        <v>68680</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3386</v>
+        <v>33186</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -541,23 +541,23 @@
         <v>200000</v>
       </c>
       <c r="D4" t="n">
-        <v>35820</v>
+        <v>39800</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8366.66</v>
+        <v>13346.66</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>27453.34</v>
+        <v>26453.34</v>
       </c>
     </row>
     <row r="5">
@@ -583,15 +583,15 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>33500</v>
+        <v>53892</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>155.2%</t>
+          <t>249.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-11920</v>
+        <v>-32312</v>
       </c>
     </row>
     <row r="6">
@@ -677,23 +677,23 @@
         <v>40000</v>
       </c>
       <c r="D8" t="n">
-        <v>26140</v>
+        <v>30120</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>20000</v>
+        <v>23386</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6140</v>
+        <v>6734</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>183290</v>
+        <v>195230</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>141.0%</t>
+          <t>150.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>177912</v>
+        <v>189852</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>31840</v>
+        <v>35820</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>31840</v>
+        <v>35820</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>66520</v>
+        <v>82440</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>62337</v>
+        <v>78257</v>
       </c>
     </row>
     <row r="13">
@@ -847,23 +847,23 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>39800</v>
+        <v>55720</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9960</v>
+        <v>34760</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>29840</v>
+        <v>20960</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>160000</v>
       </c>
       <c r="D14" t="n">
-        <v>49080</v>
+        <v>72960</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -893,11 +893,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>32370</v>
+        <v>56250</v>
       </c>
     </row>
     <row r="15">
@@ -915,23 +915,23 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>94140</v>
+        <v>128920</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>49920</v>
+        <v>56520</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>44220</v>
+        <v>72400</v>
       </c>
     </row>
     <row r="16">
@@ -957,15 +957,15 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>66228</v>
+        <v>71108</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>68548</v>
+        <v>63668</v>
       </c>
     </row>
     <row r="17">
@@ -1017,11 +1017,11 @@
         <v>50000</v>
       </c>
       <c r="D18" t="n">
-        <v>10398</v>
+        <v>20796</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>10398</v>
+        <v>20796</v>
       </c>
     </row>
     <row r="19">
@@ -1161,15 +1161,15 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>15779</v>
+        <v>16779</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>25750.9</v>
+        <v>24750.9</v>
       </c>
     </row>
     <row r="23">
@@ -1289,11 +1289,11 @@
         <v>80000</v>
       </c>
       <c r="D26" t="n">
-        <v>31840</v>
+        <v>35820</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>26860</v>
+        <v>30840</v>
       </c>
     </row>
     <row r="27">
@@ -1357,11 +1357,11 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>64920</v>
+        <v>68900</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>35120</v>
+        <v>39100</v>
       </c>
     </row>
     <row r="29">
@@ -1425,23 +1425,23 @@
         <v>100000</v>
       </c>
       <c r="D30" t="n">
-        <v>42840</v>
+        <v>55178</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>4183.33</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>42840</v>
+        <v>50994.67</v>
       </c>
     </row>
     <row r="31">
@@ -1493,11 +1493,11 @@
         <v>150000</v>
       </c>
       <c r="D32" t="n">
-        <v>56438</v>
+        <v>70418</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>34858</v>
+        <v>48838</v>
       </c>
     </row>
     <row r="33">
@@ -1527,23 +1527,23 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>115400</v>
+        <v>119380</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>7700</v>
+        <v>14200</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>107700</v>
+        <v>105180</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>26500</v>
+        <v>30480</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>14920</v>
+        <v>18900</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>114260</v>
+        <v>120860</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>65686</v>
+        <v>72286</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>58280</v>
+        <v>82080</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>48280</v>
+        <v>72080</v>
       </c>
     </row>
     <row r="37">
@@ -1671,15 +1671,15 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>20800</v>
+        <v>14200</v>
       </c>
     </row>
     <row r="38">
@@ -1697,23 +1697,23 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>112520</v>
+        <v>119120</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>24800</v>
+        <v>38550</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>87720</v>
+        <v>80570</v>
       </c>
     </row>
     <row r="39">
@@ -1867,11 +1867,11 @@
         <v>100000</v>
       </c>
       <c r="D43" t="n">
-        <v>61920</v>
+        <v>68520</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1879,11 +1879,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>57920</v>
+        <v>64520</v>
       </c>
     </row>
     <row r="44">
@@ -1969,11 +1969,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>67000</v>
+        <v>73600</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1981,11 +1981,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>42200</v>
+        <v>48800</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -541,11 +541,11 @@
         <v>200000</v>
       </c>
       <c r="D4" t="n">
-        <v>39800</v>
+        <v>35820</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -553,11 +553,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>26453.34</v>
+        <v>22473.34</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>21580</v>
+        <v>41380</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>249.7%</t>
+          <t>130.2%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-32312</v>
+        <v>-12512</v>
       </c>
     </row>
     <row r="6">
@@ -685,15 +685,15 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>23386</v>
+        <v>25775</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6734</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="9">
@@ -745,23 +745,23 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>195230</v>
+        <v>203190</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>150.2%</t>
+          <t>156.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5378</v>
+        <v>8765</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>189852</v>
+        <v>194425</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>35820</v>
+        <v>31840</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>35820</v>
+        <v>31840</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>82440</v>
+        <v>86420</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>78257</v>
+        <v>82237</v>
       </c>
     </row>
     <row r="13">
@@ -881,11 +881,11 @@
         <v>160000</v>
       </c>
       <c r="D14" t="n">
-        <v>72960</v>
+        <v>80920</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -893,11 +893,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>56250</v>
+        <v>64210</v>
       </c>
     </row>
     <row r="15">
@@ -923,15 +923,15 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>56520</v>
+        <v>59906</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>72400</v>
+        <v>69014</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>300000</v>
       </c>
       <c r="D16" t="n">
-        <v>134776</v>
+        <v>140544</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>63668</v>
+        <v>69436</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>261308.01</v>
+        <v>263288.01</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>261308.01</v>
+        <v>263288.01</v>
       </c>
     </row>
     <row r="18">
@@ -1051,23 +1051,23 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>51740</v>
+        <v>59700</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2596.6</v>
+        <v>7576.6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>49143.4</v>
+        <v>52123.4</v>
       </c>
     </row>
     <row r="20">
@@ -1119,11 +1119,11 @@
         <v>80000</v>
       </c>
       <c r="D21" t="n">
-        <v>36548</v>
+        <v>40528</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1131,11 +1131,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>33391.33</v>
+        <v>37371.33</v>
       </c>
     </row>
     <row r="22">
@@ -1255,11 +1255,11 @@
         <v>80000</v>
       </c>
       <c r="D25" t="n">
-        <v>38440</v>
+        <v>46400</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>38440</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="26">
@@ -1323,23 +1323,23 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>111684</v>
+        <v>115944</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>9880</v>
+        <v>13380</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>101804</v>
+        <v>102564</v>
       </c>
     </row>
     <row r="28">
@@ -1425,11 +1425,11 @@
         <v>100000</v>
       </c>
       <c r="D30" t="n">
-        <v>55178</v>
+        <v>59158</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>50994.67</v>
+        <v>54974.67</v>
       </c>
     </row>
     <row r="31">
@@ -1493,11 +1493,11 @@
         <v>150000</v>
       </c>
       <c r="D32" t="n">
-        <v>70418</v>
+        <v>78378</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>48838</v>
+        <v>56798</v>
       </c>
     </row>
     <row r="33">
@@ -1561,23 +1561,23 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>30480</v>
+        <v>34460</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>11580</v>
+        <v>16560</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>18900</v>
+        <v>17900</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>120860</v>
+        <v>124820</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>72286</v>
+        <v>76246</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>82080</v>
+        <v>94960</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>72080</v>
+        <v>84960</v>
       </c>
     </row>
     <row r="37">
@@ -1697,11 +1697,11 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>119120</v>
+        <v>121610</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1709,11 +1709,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>80570</v>
+        <v>83060</v>
       </c>
     </row>
     <row r="39">
@@ -1765,23 +1765,23 @@
         <v>120000</v>
       </c>
       <c r="D40" t="n">
-        <v>76108</v>
+        <v>79408</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>6000</v>
+        <v>16398</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>70108</v>
+        <v>63010</v>
       </c>
     </row>
     <row r="41">
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>13200</v>
+        <v>17200</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>-13200</v>
+        <v>-17200</v>
       </c>
     </row>
     <row r="45">
@@ -1977,15 +1977,15 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>24800</v>
+        <v>35800</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>48800</v>
+        <v>37800</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -609,11 +609,11 @@
         <v>150000</v>
       </c>
       <c r="D6" t="n">
-        <v>61740</v>
+        <v>68340</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>32757</v>
+        <v>39357</v>
       </c>
     </row>
     <row r="7">
@@ -753,15 +753,15 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8765</v>
+        <v>13745</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>194425</v>
+        <v>189445</v>
       </c>
     </row>
     <row r="11">
@@ -949,11 +949,11 @@
         <v>300000</v>
       </c>
       <c r="D16" t="n">
-        <v>140544</v>
+        <v>183920</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>69436</v>
+        <v>112812</v>
       </c>
     </row>
     <row r="17">
@@ -1051,11 +1051,11 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>59700</v>
+        <v>63680</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>52123.4</v>
+        <v>56103.4</v>
       </c>
     </row>
     <row r="20">
@@ -1153,11 +1153,11 @@
         <v>150000</v>
       </c>
       <c r="D22" t="n">
-        <v>41529.9</v>
+        <v>48129.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1165,11 +1165,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>24750.9</v>
+        <v>31350.9</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>70000</v>
       </c>
       <c r="D23" t="n">
-        <v>23688</v>
+        <v>27668</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>18708</v>
+        <v>22688</v>
       </c>
     </row>
     <row r="24">
@@ -1357,11 +1357,11 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>68900</v>
+        <v>93700</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>39100</v>
+        <v>63900</v>
       </c>
     </row>
     <row r="29">
@@ -1399,15 +1399,15 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>29800</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>64600</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="30">
@@ -1527,11 +1527,11 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>119380</v>
+        <v>123360</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>105180</v>
+        <v>109160</v>
       </c>
     </row>
     <row r="34">
@@ -1595,11 +1595,11 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>124820</v>
+        <v>139640</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>76246</v>
+        <v>91066</v>
       </c>
     </row>
     <row r="36">
@@ -1867,11 +1867,11 @@
         <v>100000</v>
       </c>
       <c r="D43" t="n">
-        <v>68520</v>
+        <v>76920</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1879,11 +1879,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>64520</v>
+        <v>72920</v>
       </c>
     </row>
     <row r="44">
@@ -1969,11 +1969,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>73600</v>
+        <v>119200</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1981,11 +1981,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>37800</v>
+        <v>83400</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -473,11 +473,11 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>170869.9</v>
+        <v>185429.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>107771.9</v>
+        <v>122331.9</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         <v>200000</v>
       </c>
       <c r="D4" t="n">
-        <v>35820</v>
+        <v>47760</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -553,11 +553,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>22473.34</v>
+        <v>34413.34</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>41380</v>
+        <v>49340</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>130.2%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-12512</v>
+        <v>-4552</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>150000</v>
       </c>
       <c r="D6" t="n">
-        <v>68340</v>
+        <v>78920</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39357</v>
+        <v>49937</v>
       </c>
     </row>
     <row r="7">
@@ -745,11 +745,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>203190</v>
+        <v>207170</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>156.3%</t>
+          <t>159.4%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>189445</v>
+        <v>193425</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>31840</v>
+        <v>35820</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>31840</v>
+        <v>35820</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>86420</v>
+        <v>90400</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>82237</v>
+        <v>86217</v>
       </c>
     </row>
     <row r="13">
@@ -915,23 +915,23 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>128920</v>
+        <v>130200</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>100.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>59906</v>
+        <v>62498</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>69014</v>
+        <v>67702</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>300000</v>
       </c>
       <c r="D16" t="n">
-        <v>183920</v>
+        <v>187708</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>112812</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="17">
@@ -983,23 +983,23 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>263288.01</v>
+        <v>267268.01</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>15988</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>263288.01</v>
+        <v>251280.01</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>50000</v>
       </c>
       <c r="D18" t="n">
-        <v>20796</v>
+        <v>22776</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>20796</v>
+        <v>22776</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>63680</v>
+        <v>79600</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>56103.4</v>
+        <v>72023.39999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1119,23 +1119,23 @@
         <v>80000</v>
       </c>
       <c r="D21" t="n">
-        <v>40528</v>
+        <v>48488</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3156.67</v>
+        <v>26956.67</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>37371.33</v>
+        <v>21531.33</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>150000</v>
       </c>
       <c r="D22" t="n">
-        <v>48129.9</v>
+        <v>60069.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1165,11 +1165,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>31350.9</v>
+        <v>43290.9</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>70000</v>
       </c>
       <c r="D23" t="n">
-        <v>27668</v>
+        <v>35628</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>22688</v>
+        <v>30648</v>
       </c>
     </row>
     <row r="24">
@@ -1255,11 +1255,11 @@
         <v>80000</v>
       </c>
       <c r="D25" t="n">
-        <v>46400</v>
+        <v>66200</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>46400</v>
+        <v>66200</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>115944</v>
+        <v>123904</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>102564</v>
+        <v>110524</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>93700</v>
+        <v>101660</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>63900</v>
+        <v>71860</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>100000</v>
       </c>
       <c r="D29" t="n">
-        <v>64600</v>
+        <v>68580</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>34800</v>
+        <v>38780</v>
       </c>
     </row>
     <row r="30">
@@ -1595,23 +1595,23 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>139640</v>
+        <v>181440</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>48574</v>
+        <v>58972</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>91066</v>
+        <v>122468</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>94960</v>
+        <v>96940</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>84960</v>
+        <v>86940</v>
       </c>
     </row>
     <row r="37">
@@ -1739,15 +1739,15 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4950</v>
+        <v>11550</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>41450</v>
+        <v>34850</v>
       </c>
     </row>
     <row r="40">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -541,11 +541,11 @@
         <v>200000</v>
       </c>
       <c r="D4" t="n">
-        <v>47760</v>
+        <v>43780</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -553,11 +553,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>34413.34</v>
+        <v>30433.34</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>49340</v>
+        <v>57300</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-4552</v>
+        <v>3408</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>150000</v>
       </c>
       <c r="D6" t="n">
-        <v>78920</v>
+        <v>82900</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>49937</v>
+        <v>53917</v>
       </c>
     </row>
     <row r="7">
@@ -651,15 +651,15 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>125.1%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2980</v>
+        <v>-2000</v>
       </c>
     </row>
     <row r="8">
@@ -711,11 +711,11 @@
         <v>30000</v>
       </c>
       <c r="D9" t="n">
-        <v>7960</v>
+        <v>3980</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>222.4%</t>
+          <t>444.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-9740</v>
+        <v>-13720</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>207170</v>
+        <v>211150</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>159.4%</t>
+          <t>162.4%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>193425</v>
+        <v>197405</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>35820</v>
+        <v>39800</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>35820</v>
+        <v>39800</v>
       </c>
     </row>
     <row r="12">
@@ -847,11 +847,11 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>55720</v>
+        <v>59700</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>20960</v>
+        <v>24940</v>
       </c>
     </row>
     <row r="14">
@@ -983,23 +983,23 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>267268.01</v>
+        <v>263288.01</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>15988</v>
+        <v>16788</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>251280.01</v>
+        <v>246500.01</v>
       </c>
     </row>
     <row r="18">
@@ -1119,11 +1119,11 @@
         <v>80000</v>
       </c>
       <c r="D21" t="n">
-        <v>48488</v>
+        <v>60428</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1131,11 +1131,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>21531.33</v>
+        <v>33471.33</v>
       </c>
     </row>
     <row r="22">
@@ -1289,23 +1289,23 @@
         <v>80000</v>
       </c>
       <c r="D26" t="n">
-        <v>35820</v>
+        <v>31840</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4980</v>
+        <v>8960</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>30840</v>
+        <v>22880</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>123904</v>
+        <v>134484</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>110524</v>
+        <v>121104</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>101660</v>
+        <v>109620</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>71860</v>
+        <v>79820</v>
       </c>
     </row>
     <row r="29">
@@ -1527,11 +1527,11 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>123360</v>
+        <v>127340</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>109160</v>
+        <v>113140</v>
       </c>
     </row>
     <row r="34">
@@ -1595,11 +1595,11 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>181440</v>
+        <v>206260</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>103.1%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>122468</v>
+        <v>147288</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>96940</v>
+        <v>67140</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>86940</v>
+        <v>57140</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>250000</v>
       </c>
       <c r="D37" t="n">
-        <v>20800</v>
+        <v>27400</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>14200</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="38">
@@ -1697,11 +1697,11 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>121610</v>
+        <v>128210</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1709,11 +1709,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>83060</v>
+        <v>89660</v>
       </c>
     </row>
     <row r="39">
@@ -1739,15 +1739,15 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>11550</v>
+        <v>41350</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>34850</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="40">
@@ -1773,15 +1773,15 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>16398</v>
+        <v>17298</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>63010</v>
+        <v>62110</v>
       </c>
     </row>
     <row r="41">
@@ -1833,11 +1833,11 @@
         <v>120000</v>
       </c>
       <c r="D42" t="n">
-        <v>21298</v>
+        <v>21698</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>21298</v>
+        <v>21698</v>
       </c>
     </row>
     <row r="43">
@@ -1943,15 +1943,15 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>20800</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>86488</v>
+        <v>65688</v>
       </c>
     </row>
     <row r="46">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -473,11 +473,11 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>185429.9</v>
+        <v>189409.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>122331.9</v>
+        <v>126311.9</v>
       </c>
     </row>
     <row r="3">
@@ -745,11 +745,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>211150</v>
+        <v>211548</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>162.4%</t>
+          <t>162.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>197405</v>
+        <v>197803</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>90400</v>
+        <v>94380</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>86217</v>
+        <v>90197</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>59700</v>
+        <v>64680</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>24940</v>
+        <v>29920</v>
       </c>
     </row>
     <row r="14">
@@ -1051,11 +1051,11 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>79600</v>
+        <v>83580</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>104.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>72023.39999999999</v>
+        <v>76003.39999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1187,11 +1187,11 @@
         <v>70000</v>
       </c>
       <c r="D23" t="n">
-        <v>35628</v>
+        <v>39608</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>30648</v>
+        <v>34628</v>
       </c>
     </row>
     <row r="24">
@@ -1561,11 +1561,11 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>34460</v>
+        <v>60940</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>17900</v>
+        <v>44380</v>
       </c>
     </row>
     <row r="35">
@@ -1697,11 +1697,11 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>128210</v>
+        <v>140210</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1709,11 +1709,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>89660</v>
+        <v>101660</v>
       </c>
     </row>
     <row r="39">
@@ -1833,11 +1833,11 @@
         <v>120000</v>
       </c>
       <c r="D42" t="n">
-        <v>21698</v>
+        <v>21998</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>21698</v>
+        <v>21998</v>
       </c>
     </row>
     <row r="43">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -677,11 +677,11 @@
         <v>40000</v>
       </c>
       <c r="D8" t="n">
-        <v>30120</v>
+        <v>31800</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4345</v>
+        <v>6025</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>211548</v>
+        <v>219508</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>162.7%</t>
+          <t>168.9%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>197803</v>
+        <v>205763</v>
       </c>
     </row>
     <row r="11">
@@ -847,11 +847,11 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>64680</v>
+        <v>68660</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>29920</v>
+        <v>33900</v>
       </c>
     </row>
     <row r="14">
@@ -1051,11 +1051,11 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>83580</v>
+        <v>91540</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>104.5%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>76003.39999999999</v>
+        <v>83963.39999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1153,11 +1153,11 @@
         <v>150000</v>
       </c>
       <c r="D22" t="n">
-        <v>60069.9</v>
+        <v>68029.89999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1165,11 +1165,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>43290.9</v>
+        <v>51250.89999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1255,11 +1255,11 @@
         <v>80000</v>
       </c>
       <c r="D25" t="n">
-        <v>66200</v>
+        <v>70180</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>66200</v>
+        <v>70180</v>
       </c>
     </row>
     <row r="26">
@@ -1357,11 +1357,11 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>109620</v>
+        <v>113600</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>79820</v>
+        <v>83800</v>
       </c>
     </row>
     <row r="29">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,20 +439,30 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>协同业绩(元)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>完成率(含协同)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>完成率</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>本月退费</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>退费率</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>本月净流水</t>
         </is>
@@ -475,20 +485,28 @@
       <c r="D2" t="n">
         <v>189409.9</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>65.8%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>63.1%</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>63098</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>126311.9</v>
       </c>
     </row>
@@ -509,20 +527,28 @@
       <c r="D3" t="n">
         <v>68680</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>34.3%</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>34.3%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>33186</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>48.3%</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>35494</v>
       </c>
     </row>
@@ -543,20 +569,28 @@
       <c r="D4" t="n">
         <v>43780</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>21.9%</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>21.9%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>13346.66</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>30.5%</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>30433.34</v>
       </c>
     </row>
@@ -577,20 +611,28 @@
       <c r="D5" t="n">
         <v>57300</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>4988</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>41.5%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>38.2%</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>53892</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>94.1%</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>3408</v>
       </c>
     </row>
@@ -611,20 +653,28 @@
       <c r="D6" t="n">
         <v>82900</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>55.3%</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>55.3%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>28983</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>35.0%</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>53917</v>
       </c>
     </row>
@@ -645,20 +695,28 @@
       <c r="D7" t="n">
         <v>7960</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>26.5%</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>26.5%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>9960</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>125.1%</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>-2000</v>
       </c>
     </row>
@@ -679,20 +737,28 @@
       <c r="D8" t="n">
         <v>31800</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>79.5%</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>79.5%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>25775</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>81.1%</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>6025</v>
       </c>
     </row>
@@ -713,20 +779,28 @@
       <c r="D9" t="n">
         <v>3980</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>13.3%</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>17700</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>444.7%</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>-13720</v>
       </c>
     </row>
@@ -747,20 +821,28 @@
       <c r="D10" t="n">
         <v>219508</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>173.5%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>168.9%</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>13745</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>6.3%</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>205763</v>
       </c>
     </row>
@@ -781,20 +863,28 @@
       <c r="D11" t="n">
         <v>39800</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>39.8%</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>39.8%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>39800</v>
       </c>
     </row>
@@ -815,20 +905,28 @@
       <c r="D12" t="n">
         <v>94380</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>30198</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>95.8%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>72.6%</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="H12" t="n">
         <v>4183</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>4.4%</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>90197</v>
       </c>
     </row>
@@ -849,20 +947,28 @@
       <c r="D13" t="n">
         <v>68660</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>45.8%</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>34760</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>50.6%</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>33900</v>
       </c>
     </row>
@@ -883,20 +989,28 @@
       <c r="D14" t="n">
         <v>80920</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>50.6%</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>50.6%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>16710</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>20.7%</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>64210</v>
       </c>
     </row>
@@ -917,20 +1031,28 @@
       <c r="D15" t="n">
         <v>130200</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>107.8%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>100.2%</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>62498</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>48.0%</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>67702</v>
       </c>
     </row>
@@ -951,20 +1073,28 @@
       <c r="D16" t="n">
         <v>187708</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="n">
+        <v>158352</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>115.4%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>62.6%</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
         <v>71108</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>37.9%</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>116600</v>
       </c>
     </row>
@@ -985,20 +1115,28 @@
       <c r="D17" t="n">
         <v>263288.01</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>87.8%</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>87.8%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>16788</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>6.4%</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>246500.01</v>
       </c>
     </row>
@@ -1019,20 +1157,28 @@
       <c r="D18" t="n">
         <v>22776</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>45.6%</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>45.6%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>22776</v>
       </c>
     </row>
@@ -1053,20 +1199,28 @@
       <c r="D19" t="n">
         <v>91540</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>114.4%</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>114.4%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
         <v>7576.6</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>8.3%</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>83963.39999999999</v>
       </c>
     </row>
@@ -1087,20 +1241,28 @@
       <c r="D20" t="n">
         <v>15728</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>19.7%</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>19.7%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>4150</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>26.4%</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>11578</v>
       </c>
     </row>
@@ -1121,20 +1283,28 @@
       <c r="D21" t="n">
         <v>60428</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>75.5%</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>75.5%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
         <v>26956.67</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>44.6%</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>33471.33</v>
       </c>
     </row>
@@ -1155,20 +1325,28 @@
       <c r="D22" t="n">
         <v>68029.89999999999</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" t="n">
+        <v>45600</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>75.8%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>45.4%</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="H22" t="n">
         <v>16779</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>24.7%</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>51250.89999999999</v>
       </c>
     </row>
@@ -1189,20 +1367,28 @@
       <c r="D23" t="n">
         <v>39608</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" t="n">
+        <v>12598</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>74.6%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>56.6%</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="H23" t="n">
         <v>4980</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>12.6%</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>34628</v>
       </c>
     </row>
@@ -1223,20 +1409,28 @@
       <c r="D24" t="n">
         <v>7768</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>9.7%</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>9.7%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
         <v>4980</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>64.1%</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>2788</v>
       </c>
     </row>
@@ -1257,20 +1451,28 @@
       <c r="D25" t="n">
         <v>70180</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>87.7%</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>87.7%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>70180</v>
       </c>
     </row>
@@ -1291,20 +1493,28 @@
       <c r="D26" t="n">
         <v>31840</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>39.8%</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>39.8%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
         <v>8960</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>28.1%</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>22880</v>
       </c>
     </row>
@@ -1325,20 +1535,28 @@
       <c r="D27" t="n">
         <v>134484</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>53.8%</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
         <v>13380</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>9.9%</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>121104</v>
       </c>
     </row>
@@ -1359,20 +1577,28 @@
       <c r="D28" t="n">
         <v>113600</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>56.8%</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>56.8%</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
         <v>29800</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>26.2%</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>83800</v>
       </c>
     </row>
@@ -1393,20 +1619,28 @@
       <c r="D29" t="n">
         <v>68580</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>68.6%</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>68.6%</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
         <v>29800</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>43.5%</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>38780</v>
       </c>
     </row>
@@ -1427,20 +1661,28 @@
       <c r="D30" t="n">
         <v>59158</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>59.2%</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>59.2%</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
         <v>4183.33</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>7.1%</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>54974.67</v>
       </c>
     </row>
@@ -1461,20 +1703,28 @@
       <c r="D31" t="n">
         <v>51420</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>34.3%</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>34.3%</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
         <v>17000</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>33.1%</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>34420</v>
       </c>
     </row>
@@ -1495,20 +1745,28 @@
       <c r="D32" t="n">
         <v>78378</v>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>52.3%</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52.3%</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
         <v>21580</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>27.5%</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>56798</v>
       </c>
     </row>
@@ -1529,20 +1787,28 @@
       <c r="D33" t="n">
         <v>127340</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>74.9%</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>74.9%</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
         <v>14200</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>11.2%</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>113140</v>
       </c>
     </row>
@@ -1563,20 +1829,28 @@
       <c r="D34" t="n">
         <v>60940</v>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" t="n">
+        <v>18796</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>99.7%</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>76.2%</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>16560</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>27.2%</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>44380</v>
       </c>
     </row>
@@ -1597,20 +1871,28 @@
       <c r="D35" t="n">
         <v>206260</v>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>103.1%</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>103.1%</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
         <v>58972</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>28.6%</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>147288</v>
       </c>
     </row>
@@ -1631,20 +1913,28 @@
       <c r="D36" t="n">
         <v>67140</v>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>33.6%</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>33.6%</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
         <v>10000</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>14.9%</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>57140</v>
       </c>
     </row>
@@ -1665,20 +1955,28 @@
       <c r="D37" t="n">
         <v>27400</v>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>11.0%</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>11.0%</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
         <v>6600</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>24.1%</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>20800</v>
       </c>
     </row>
@@ -1699,20 +1997,28 @@
       <c r="D38" t="n">
         <v>140210</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>83.5%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>77.9%</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="H38" t="n">
         <v>38550</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>27.5%</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>101660</v>
       </c>
     </row>
@@ -1733,20 +2039,28 @@
       <c r="D39" t="n">
         <v>46400</v>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>46.4%</t>
         </is>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>46.4%</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
         <v>41350</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>89.1%</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>5050</v>
       </c>
     </row>
@@ -1767,20 +2081,28 @@
       <c r="D40" t="n">
         <v>79408</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>66.2%</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>66.2%</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
         <v>17298</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>21.8%</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>62110</v>
       </c>
     </row>
@@ -1801,20 +2123,28 @@
       <c r="D41" t="n">
         <v>33380</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" t="n">
+        <v>39588</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>60.8%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>27.8%</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>33380</v>
       </c>
     </row>
@@ -1835,20 +2165,28 @@
       <c r="D42" t="n">
         <v>21998</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" t="n">
+        <v>49218</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>59.3%</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>18.3%</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>21998</v>
       </c>
     </row>
@@ -1869,20 +2207,28 @@
       <c r="D43" t="n">
         <v>76920</v>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" t="n">
+        <v>16398</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>93.3%</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>76.9%</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="H43" t="n">
         <v>4000</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>5.2%</t>
         </is>
       </c>
-      <c r="H43" t="n">
+      <c r="J43" t="n">
         <v>72920</v>
       </c>
     </row>
@@ -1903,20 +2249,28 @@
       <c r="D44" t="n">
         <v>0</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
         <v>17200</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>-17200</v>
       </c>
     </row>
@@ -1937,20 +2291,28 @@
       <c r="D45" t="n">
         <v>86488</v>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>86.5%</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>86.5%</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
         <v>20800</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>24.0%</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>65688</v>
       </c>
     </row>
@@ -1971,20 +2333,28 @@
       <c r="D46" t="n">
         <v>119200</v>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" t="n">
+        <v>30398</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>136.0%</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>108.4%</t>
         </is>
       </c>
-      <c r="F46" t="n">
+      <c r="H46" t="n">
         <v>35800</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>30.0%</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
         <v>83400</v>
       </c>
     </row>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>189409.9</v>
+        <v>220309.9</v>
       </c>
       <c r="E2" t="n">
         <v>8000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>126311.9</v>
+        <v>157211.9</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>200000</v>
       </c>
       <c r="D3" t="n">
-        <v>68680</v>
+        <v>119260</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>35494</v>
+        <v>86074</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>200000</v>
       </c>
       <c r="D4" t="n">
-        <v>43780</v>
+        <v>48760</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>30433.34</v>
+        <v>35413.34</v>
       </c>
     </row>
     <row r="5">
@@ -609,19 +609,19 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>57300</v>
+        <v>71240</v>
       </c>
       <c r="E5" t="n">
         <v>4988</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3408</v>
+        <v>17348</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>150000</v>
       </c>
       <c r="D6" t="n">
-        <v>82900</v>
+        <v>149660</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>53917</v>
+        <v>120677</v>
       </c>
     </row>
     <row r="7">
@@ -819,31 +819,31 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>219508</v>
+        <v>227468</v>
       </c>
       <c r="E10" t="n">
         <v>6000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>173.5%</t>
+          <t>179.6%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>168.9%</t>
+          <t>175.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>13745</v>
+        <v>17894</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>205763</v>
+        <v>209574</v>
       </c>
     </row>
     <row r="11">
@@ -861,19 +861,19 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>39800</v>
+        <v>64700</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>39800</v>
+        <v>64700</v>
       </c>
     </row>
     <row r="12">
@@ -903,19 +903,19 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>94380</v>
+        <v>99360</v>
       </c>
       <c r="E12" t="n">
         <v>30198</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -923,11 +923,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>90197</v>
+        <v>95177</v>
       </c>
     </row>
     <row r="13">
@@ -945,19 +945,19 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>68660</v>
+        <v>81600</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -965,11 +965,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>33900</v>
+        <v>46840</v>
       </c>
     </row>
     <row r="14">
@@ -987,19 +987,19 @@
         <v>160000</v>
       </c>
       <c r="D14" t="n">
-        <v>80920</v>
+        <v>93860</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>64210</v>
+        <v>77150</v>
       </c>
     </row>
     <row r="15">
@@ -1029,19 +1029,19 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>130200</v>
+        <v>135180</v>
       </c>
       <c r="E15" t="n">
         <v>10000</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>111.7%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>100.2%</t>
+          <t>104.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1049,11 +1049,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>67702</v>
+        <v>72682</v>
       </c>
     </row>
     <row r="16">
@@ -1113,19 +1113,19 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>263288.01</v>
+        <v>267088.01</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>246500.01</v>
+        <v>250300.01</v>
       </c>
     </row>
     <row r="18">
@@ -1197,19 +1197,19 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>91540</v>
+        <v>95520</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>119.4%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>119.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>83963.39999999999</v>
+        <v>87943.39999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1281,19 +1281,19 @@
         <v>80000</v>
       </c>
       <c r="D21" t="n">
-        <v>60428</v>
+        <v>68388</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>33471.33</v>
+        <v>41431.33</v>
       </c>
     </row>
     <row r="22">
@@ -1323,31 +1323,31 @@
         <v>150000</v>
       </c>
       <c r="D22" t="n">
-        <v>68029.89999999999</v>
+        <v>72009.89999999999</v>
       </c>
       <c r="E22" t="n">
         <v>45600</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>16779</v>
+        <v>20929</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>51250.89999999999</v>
+        <v>51080.89999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1365,31 +1365,31 @@
         <v>70000</v>
       </c>
       <c r="D23" t="n">
-        <v>39608</v>
+        <v>43588</v>
       </c>
       <c r="E23" t="n">
         <v>12598</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4980</v>
+        <v>7761.2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>34628</v>
+        <v>35826.8</v>
       </c>
     </row>
     <row r="24">
@@ -1449,19 +1449,19 @@
         <v>80000</v>
       </c>
       <c r="D25" t="n">
-        <v>70180</v>
+        <v>74160</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>70180</v>
+        <v>74160</v>
       </c>
     </row>
     <row r="26">
@@ -1575,19 +1575,19 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>113600</v>
+        <v>148440</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>83800</v>
+        <v>118640</v>
       </c>
     </row>
     <row r="29">
@@ -1617,19 +1617,19 @@
         <v>100000</v>
       </c>
       <c r="D29" t="n">
-        <v>68580</v>
+        <v>89382</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>38780</v>
+        <v>59582</v>
       </c>
     </row>
     <row r="30">
@@ -1743,31 +1743,31 @@
         <v>150000</v>
       </c>
       <c r="D32" t="n">
-        <v>78378</v>
+        <v>88338</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>21580</v>
+        <v>23174</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>56798</v>
+        <v>65164</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>127340</v>
+        <v>147140</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>113140</v>
+        <v>132940</v>
       </c>
     </row>
     <row r="34">
@@ -1827,19 +1827,19 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>60940</v>
+        <v>65920</v>
       </c>
       <c r="E34" t="n">
         <v>18796</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>105.9%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1847,11 +1847,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>44380</v>
+        <v>49360</v>
       </c>
     </row>
     <row r="35">
@@ -1869,19 +1869,19 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>206260</v>
+        <v>251860</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>103.1%</t>
+          <t>125.9%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>103.1%</t>
+          <t>125.9%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1889,11 +1889,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>147288</v>
+        <v>192888</v>
       </c>
     </row>
     <row r="36">
@@ -1911,31 +1911,31 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>67140</v>
+        <v>213920</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10000</v>
+        <v>46588</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>57140</v>
+        <v>167332</v>
       </c>
     </row>
     <row r="37">
@@ -1953,19 +1953,19 @@
         <v>250000</v>
       </c>
       <c r="D37" t="n">
-        <v>27400</v>
+        <v>103000</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1973,11 +1973,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>20800</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="38">
@@ -1995,19 +1995,19 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>140210</v>
+        <v>187310</v>
       </c>
       <c r="E38" t="n">
         <v>10000</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>104.1%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>101660</v>
+        <v>148760</v>
       </c>
     </row>
     <row r="39">
@@ -2079,19 +2079,19 @@
         <v>120000</v>
       </c>
       <c r="D40" t="n">
-        <v>79408</v>
+        <v>106228</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2099,11 +2099,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>62110</v>
+        <v>88930</v>
       </c>
     </row>
     <row r="41">
@@ -2163,19 +2163,19 @@
         <v>120000</v>
       </c>
       <c r="D42" t="n">
-        <v>21998</v>
+        <v>29998</v>
       </c>
       <c r="E42" t="n">
         <v>49218</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>21998</v>
+        <v>29998</v>
       </c>
     </row>
     <row r="43">
@@ -2205,19 +2205,19 @@
         <v>100000</v>
       </c>
       <c r="D43" t="n">
-        <v>76920</v>
+        <v>90120</v>
       </c>
       <c r="E43" t="n">
         <v>16398</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>106.5%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>72920</v>
+        <v>86120</v>
       </c>
     </row>
     <row r="44">
@@ -2289,31 +2289,31 @@
         <v>100000</v>
       </c>
       <c r="D45" t="n">
-        <v>86488</v>
+        <v>96488</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>20800</v>
+        <v>50600</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>65688</v>
+        <v>45888</v>
       </c>
     </row>
     <row r="46">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,34 +480,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>300000</v>
+        <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>220309.9</v>
+        <v>29780</v>
       </c>
       <c r="E2" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>63098</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>157211.9</v>
+        <v>29780</v>
       </c>
     </row>
     <row r="3">
@@ -518,38 +518,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>闫丽东</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200000</v>
+        <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>119260</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>33186</v>
+        <v>2589</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>86074</v>
+        <v>-2589</v>
       </c>
     </row>
     <row r="4">
@@ -560,38 +560,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>唐歌</t>
+          <t>闫丽东</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>48760</v>
+        <v>9960</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>13346.66</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>35413.34</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="5">
@@ -602,38 +602,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>何媛媛</t>
+          <t>唐歌</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>71240</v>
+        <v>19920</v>
       </c>
       <c r="E5" t="n">
-        <v>4988</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>53892</v>
+        <v>3700</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17348</v>
+        <v>16220</v>
       </c>
     </row>
     <row r="6">
@@ -644,240 +644,240 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>何媛媛</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>149660</v>
+        <v>4980</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>28983</v>
+        <v>1680</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>120677</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>刘学锟</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30000</v>
+        <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>7960</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>9960</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>李洋洋</t>
+          <t>关万辉</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40000</v>
+        <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>31800</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>25775</v>
+        <v>6600</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6025</v>
+        <v>-6600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>张露</t>
+          <t>郑理</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30000</v>
+        <v>80000</v>
       </c>
       <c r="D9" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>17700</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>444.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-13720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>肖伟</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>227468</v>
+        <v>16560</v>
       </c>
       <c r="E10" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>179.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>175.0%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>17894</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>209574</v>
+        <v>16560</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>黄梦妹</t>
+          <t>刘士明</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>64700</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -885,293 +885,293 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>64700</v>
+        <v>-3980</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>130000</v>
+        <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>99360</v>
+        <v>10000</v>
       </c>
       <c r="E12" t="n">
-        <v>30198</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4183</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>95177</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>81600</v>
+        <v>1980</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>34760</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>46840</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>160000</v>
+        <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>93860</v>
+        <v>30000</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>16710</v>
+        <v>6600</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>77150</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>郑美琦</t>
+          <t>李天阳</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>130000</v>
+        <v>80000</v>
       </c>
       <c r="D15" t="n">
-        <v>135180</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>111.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>104.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>62498</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>72682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>梁志超</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>300000</v>
+        <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>187708</v>
+        <v>24800</v>
       </c>
       <c r="E16" t="n">
-        <v>158352</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>115.4%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>71108</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>116600</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>丁蕾</t>
+          <t>安百柠</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>300000</v>
+        <v>80000</v>
       </c>
       <c r="D17" t="n">
-        <v>267088.01</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>16788</v>
+        <v>45600</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>250300.01</v>
+        <v>-45600</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周紫姻</t>
+          <t>姜人荷</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>50000</v>
+        <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>22776</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1179,289 +1179,289 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>22776</v>
+        <v>-5000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>冯岚</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>80000</v>
+        <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>95520</v>
+        <v>27800</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7576.6</v>
+        <v>16600</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>87943.39999999999</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>段继宇</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>80000</v>
+        <v>88000</v>
       </c>
       <c r="D20" t="n">
-        <v>15728</v>
+        <v>6600</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4150</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>11578</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>樊帆</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>80000</v>
+        <v>88000</v>
       </c>
       <c r="D21" t="n">
-        <v>68388</v>
+        <v>10000</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>26956.67</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>41431.33</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>龙少海</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="D22" t="n">
-        <v>72009.89999999999</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>45600</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>20929</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>51080.89999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>70000</v>
+        <v>80000</v>
       </c>
       <c r="D23" t="n">
-        <v>43588</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>12598</v>
+        <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>7761.2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>35826.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>王蓉</t>
+          <t>张天昂</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>80000</v>
+        <v>88000</v>
       </c>
       <c r="D24" t="n">
-        <v>7768</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>74160</v>
+        <v>398</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1473,889 +1473,679 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>74160</v>
+        <v>398</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>闫文奇</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>80000</v>
+        <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>31840</v>
+        <v>23338</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>8960</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>22880</v>
+        <v>23338</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>黄梦妹</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>250000</v>
+        <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>134484</v>
+        <v>4980</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>13380</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>121104</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>郑美琦</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>200000</v>
+        <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>148440</v>
+        <v>4980</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>29800</v>
+        <v>18600</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>373.5%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>118640</v>
+        <v>-13620</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>高铭瑞</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>100000</v>
+        <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>89382</v>
+        <v>4980</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>29800</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>59582</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>100000</v>
+        <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>59158</v>
+        <v>3980</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4183.33</v>
+        <v>8000</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>201.0%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>54974.67</v>
+        <v>-4020</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>关万辉</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>51420</v>
+        <v>36400</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>17000</v>
+        <v>8600</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>34420</v>
+        <v>27800</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>刘士明</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>88338</v>
+        <v>12000</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>23174</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>65164</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>高铭瑞</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>170000</v>
+        <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>147140</v>
+        <v>3980</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>14200</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>132940</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>郑理</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>65920</v>
+        <v>22719</v>
       </c>
       <c r="E34" t="n">
-        <v>18796</v>
+        <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>105.9%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>16560</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>49360</v>
+        <v>22719</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>251860</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>125.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>125.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>58972</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>192888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>200000</v>
+        <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>213920</v>
+        <v>9960</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>46588</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>167332</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>250000</v>
+        <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>103000</v>
+        <v>9960</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>96400</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>丁蕾</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>180000</v>
+        <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>187310</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>104.1%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>38550</v>
+        <v>29800</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>148760</v>
+        <v>-29800</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>李天阳</t>
+          <t>梁志超</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>100000</v>
+        <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>46400</v>
+        <v>7760</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>41350</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>5050</v>
+        <v>7760</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>姜人荷</t>
+          <t>周紫姻</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="D40" t="n">
-        <v>106228</v>
+        <v>3800</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>17298</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>88930</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>安百柠</t>
+          <t>李洋洋</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>33380</v>
+        <v>8960</v>
       </c>
       <c r="E41" t="n">
-        <v>39588</v>
+        <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>33380</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>班主任</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>冯岚</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>120000</v>
-      </c>
-      <c r="D42" t="n">
-        <v>29998</v>
-      </c>
-      <c r="E42" t="n">
-        <v>49218</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>66.0%</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>29998</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>班主任</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>郑鲁</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D43" t="n">
-        <v>90120</v>
-      </c>
-      <c r="E43" t="n">
-        <v>16398</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>106.5%</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>90.1%</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>86120</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>班主任</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>张天昂</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>17200</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>-17200</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>班主任</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>周玉枝</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D45" t="n">
-        <v>96488</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>96.5%</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>96.5%</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>50600</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>52.4%</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>45888</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>班主任</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>龙少海</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>110000</v>
-      </c>
-      <c r="D46" t="n">
-        <v>119200</v>
-      </c>
-      <c r="E46" t="n">
-        <v>30398</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>136.0%</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>108.4%</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>35800</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>83400</v>
+        <v>7280</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>29780</v>
+        <v>75380</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>29780</v>
+        <v>75380</v>
       </c>
     </row>
     <row r="3">
@@ -537,11 +537,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2589</v>
+        <v>19389</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-2589</v>
+        <v>-19389</v>
       </c>
     </row>
     <row r="4">
@@ -579,19 +579,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>11580</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>116.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9960</v>
+        <v>-1620</v>
       </c>
     </row>
     <row r="5">
@@ -609,19 +609,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>19920</v>
+        <v>24900</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16220</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="6">
@@ -693,19 +693,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="8">
@@ -747,11 +747,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6600</v>
+        <v>10750</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-6600</v>
+        <v>-10750</v>
       </c>
     </row>
     <row r="9">
@@ -819,19 +819,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>16560</v>
+        <v>21540</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16560</v>
+        <v>21540</v>
       </c>
     </row>
     <row r="11">
@@ -861,19 +861,19 @@
         <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>11640</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -881,11 +881,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-3980</v>
+        <v>7660</v>
       </c>
     </row>
     <row r="12">
@@ -903,31 +903,31 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>10000</v>
+        <v>12490</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10000</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="13">
@@ -945,19 +945,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>1980</v>
+        <v>91380</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>114.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>114.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1980</v>
+        <v>91380</v>
       </c>
     </row>
     <row r="14">
@@ -987,31 +987,31 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>30000</v>
+        <v>33800</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6600</v>
+        <v>13200</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>23400</v>
+        <v>20600</v>
       </c>
     </row>
     <row r="15">
@@ -1071,31 +1071,31 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>24800</v>
+        <v>28760</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>24800</v>
+        <v>22160</v>
       </c>
     </row>
     <row r="17">
@@ -1155,31 +1155,31 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>13980</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5000</v>
+        <v>17000</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>121.6%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-5000</v>
+        <v>-3020</v>
       </c>
     </row>
     <row r="19">
@@ -1209,19 +1209,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>16600</v>
+        <v>34000</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>11200</v>
+        <v>-6200</v>
       </c>
     </row>
     <row r="20">
@@ -1365,19 +1365,19 @@
         <v>80000</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>55600</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>55600</v>
       </c>
     </row>
     <row r="24">
@@ -1449,31 +1449,31 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>398</v>
+        <v>10796</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>398</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="26">
@@ -1503,19 +1503,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>23338</v>
+        <v>16738</v>
       </c>
     </row>
     <row r="27">
@@ -1659,31 +1659,31 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>3980</v>
+        <v>7960</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>201.0%</t>
+          <t>150.8%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>-4020</v>
+        <v>-4040</v>
       </c>
     </row>
     <row r="31">
@@ -1701,31 +1701,31 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>36400</v>
+        <v>50570</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>8600</v>
+        <v>13100</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>27800</v>
+        <v>37470</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>12000</v>
+        <v>16980</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>12000</v>
+        <v>16980</v>
       </c>
     </row>
     <row r="33">
@@ -1785,31 +1785,31 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>3980</v>
+        <v>15980</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>3980</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="34">
@@ -1827,19 +1827,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>22719</v>
+        <v>32679</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>22719</v>
+        <v>32679</v>
       </c>
     </row>
     <row r="35">
@@ -1869,19 +1869,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>19920</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>19920</v>
       </c>
     </row>
     <row r="36">
@@ -1923,19 +1923,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>9960</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="37">
@@ -1953,19 +1953,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="38">
@@ -2007,11 +2007,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>29800</v>
+        <v>43708</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>-29800</v>
+        <v>-43708</v>
       </c>
     </row>
     <row r="39">
@@ -2037,19 +2037,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>7760</v>
+        <v>11560</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>7760</v>
+        <v>11560</v>
       </c>
     </row>
     <row r="40">
@@ -2079,19 +2079,19 @@
         <v>40000</v>
       </c>
       <c r="D40" t="n">
-        <v>3800</v>
+        <v>8780</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>3800</v>
+        <v>8780</v>
       </c>
     </row>
     <row r="41">
@@ -2121,19 +2121,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>8960</v>
+        <v>18920</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2141,11 +2141,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>7280</v>
+        <v>17240</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -567,19 +567,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>116.3%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-1620</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="5">
@@ -651,19 +651,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>4980</v>
+        <v>36440</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3300</v>
+        <v>34760</v>
       </c>
     </row>
     <row r="7">
@@ -693,19 +693,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>9960</v>
+        <v>24900</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9960</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="8">
@@ -735,31 +735,31 @@
         <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>11580</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>10750</v>
+        <v>17350</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>149.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-10750</v>
+        <v>-5770</v>
       </c>
     </row>
     <row r="9">
@@ -777,19 +777,19 @@
         <v>80000</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="10">
@@ -819,19 +819,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>21540</v>
+        <v>31500</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>21540</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="11">
@@ -861,19 +861,19 @@
         <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>11640</v>
+        <v>21600</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -881,11 +881,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7660</v>
+        <v>17620</v>
       </c>
     </row>
     <row r="12">
@@ -987,19 +987,19 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>33800</v>
+        <v>63600</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>20600</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="15">
@@ -1071,19 +1071,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>28760</v>
+        <v>32540</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>22160</v>
+        <v>25940</v>
       </c>
     </row>
     <row r="17">
@@ -1197,19 +1197,19 @@
         <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>27800</v>
+        <v>39800</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>85.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-6200</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="20">
@@ -1239,19 +1239,19 @@
         <v>88000</v>
       </c>
       <c r="D20" t="n">
-        <v>6600</v>
+        <v>41220</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6600</v>
+        <v>41220</v>
       </c>
     </row>
     <row r="21">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="23">
@@ -1449,19 +1449,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>10796</v>
+        <v>15776</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>4196</v>
+        <v>9176</v>
       </c>
     </row>
     <row r="26">
@@ -1491,31 +1491,31 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>23338</v>
+        <v>53218</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6600</v>
+        <v>9786</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>16738</v>
+        <v>43432</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>4980</v>
+        <v>19920</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>4980</v>
+        <v>19920</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>4980</v>
+        <v>14940</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>373.5%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-13620</v>
+        <v>-3660</v>
       </c>
     </row>
     <row r="29">
@@ -1617,19 +1617,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>4980</v>
+        <v>19920</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>4980</v>
+        <v>19920</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>7960</v>
+        <v>17920</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>150.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>-4040</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="31">
@@ -1701,19 +1701,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>50570</v>
+        <v>64250</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>37470</v>
+        <v>51150</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>16980</v>
+        <v>28980</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>16980</v>
+        <v>28980</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>15980</v>
+        <v>21161</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>11000</v>
+        <v>16181</v>
       </c>
     </row>
     <row r="34">
@@ -1911,19 +1911,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>9960</v>
+        <v>16958</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>5980</v>
+        <v>12978</v>
       </c>
     </row>
     <row r="37">
@@ -2007,11 +2007,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>43708</v>
+        <v>85708</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>-43708</v>
+        <v>-85708</v>
       </c>
     </row>
     <row r="39">
@@ -2037,19 +2037,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>11560</v>
+        <v>51148</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>11560</v>
+        <v>51148</v>
       </c>
     </row>
     <row r="40">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -567,19 +567,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>14940</v>
+        <v>21420</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3360</v>
+        <v>9840</v>
       </c>
     </row>
     <row r="5">
@@ -609,19 +609,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>24900</v>
+        <v>34900</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>21200</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="6">
@@ -693,19 +693,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>24900</v>
+        <v>54820</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>24900</v>
+        <v>54820</v>
       </c>
     </row>
     <row r="8">
@@ -777,19 +777,19 @@
         <v>80000</v>
       </c>
       <c r="D9" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="10">
@@ -819,31 +819,31 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>31500</v>
+        <v>51460</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>31500</v>
+        <v>47480</v>
       </c>
     </row>
     <row r="11">
@@ -861,19 +861,19 @@
         <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>21600</v>
+        <v>31560</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -881,11 +881,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17620</v>
+        <v>27580</v>
       </c>
     </row>
     <row r="12">
@@ -987,19 +987,19 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>63600</v>
+        <v>65600</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>50400</v>
+        <v>52400</v>
       </c>
     </row>
     <row r="15">
@@ -1071,19 +1071,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>32540</v>
+        <v>52340</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>25940</v>
+        <v>45740</v>
       </c>
     </row>
     <row r="17">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1000</v>
+        <v>7600</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-1000</v>
+        <v>-7600</v>
       </c>
     </row>
     <row r="23">
@@ -1365,19 +1365,19 @@
         <v>80000</v>
       </c>
       <c r="D23" t="n">
-        <v>55600</v>
+        <v>57580</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>55600</v>
+        <v>57580</v>
       </c>
     </row>
     <row r="24">
@@ -1461,19 +1461,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6600</v>
+        <v>9090</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>9176</v>
+        <v>6686</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>53218</v>
+        <v>64798</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1511,11 +1511,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>43432</v>
+        <v>55012</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>19920</v>
+        <v>24900</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>19920</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="28">
@@ -1617,31 +1617,31 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>19920</v>
+        <v>29880</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>19920</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>17920</v>
+        <v>32860</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>5920</v>
+        <v>20860</v>
       </c>
     </row>
     <row r="31">
@@ -1701,19 +1701,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>64250</v>
+        <v>76848</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>51150</v>
+        <v>63748</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>28980</v>
+        <v>48780</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>28980</v>
+        <v>48780</v>
       </c>
     </row>
     <row r="33">
@@ -1911,19 +1911,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>16958</v>
+        <v>25738</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>12978</v>
+        <v>21758</v>
       </c>
     </row>
     <row r="37">
@@ -2037,19 +2037,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>51148</v>
+        <v>71748</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>51148</v>
+        <v>71748</v>
       </c>
     </row>
     <row r="40">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -495,19 +495,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>75380</v>
+        <v>70400</v>
       </c>
     </row>
     <row r="3">
@@ -693,31 +693,31 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>54820</v>
+        <v>59800</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>54820</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="8">
@@ -819,19 +819,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>51460</v>
+        <v>51858</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47480</v>
+        <v>47878</v>
       </c>
     </row>
     <row r="11">
@@ -945,19 +945,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>91380</v>
+        <v>129020</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>114.2%</t>
+          <t>161.3%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>114.2%</t>
+          <t>161.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>91380</v>
+        <v>129020</v>
       </c>
     </row>
     <row r="14">
@@ -1323,19 +1323,19 @@
         <v>80000</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-7600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="23">
@@ -1449,19 +1449,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>15776</v>
+        <v>21154</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>6686</v>
+        <v>12064</v>
       </c>
     </row>
     <row r="26">
@@ -1659,19 +1659,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>32860</v>
+        <v>37840</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>20860</v>
+        <v>25840</v>
       </c>
     </row>
     <row r="31">
@@ -1701,19 +1701,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>76848</v>
+        <v>127248</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>63748</v>
+        <v>114148</v>
       </c>
     </row>
     <row r="32">
@@ -1827,19 +1827,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>32679</v>
+        <v>42679</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>32679</v>
+        <v>42679</v>
       </c>
     </row>
     <row r="35">
@@ -1869,19 +1869,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>19920</v>
+        <v>23720</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>19920</v>
+        <v>23720</v>
       </c>
     </row>
     <row r="36">
@@ -1911,19 +1911,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>25738</v>
+        <v>35738</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>21758</v>
+        <v>31758</v>
       </c>
     </row>
     <row r="37">
@@ -1965,19 +1965,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>14940</v>
+        <v>10960</v>
       </c>
     </row>
     <row r="38">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,31 +483,31 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>75380</v>
+        <v>91940</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4980</v>
+        <v>8366.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>70400</v>
+        <v>83573.34</v>
       </c>
     </row>
     <row r="3">
@@ -609,31 +609,31 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>34900</v>
+        <v>54820</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3700</v>
+        <v>6397.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>31200</v>
+        <v>48422.5</v>
       </c>
     </row>
     <row r="6">
@@ -747,19 +747,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>17350</v>
+        <v>47150</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>149.8%</t>
+          <t>407.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-5770</v>
+        <v>-35570</v>
       </c>
     </row>
     <row r="9">
@@ -789,19 +789,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14940</v>
+        <v>10960</v>
       </c>
     </row>
     <row r="10">
@@ -987,31 +987,31 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>65600</v>
+        <v>75600</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>13200</v>
+        <v>15000</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>52400</v>
+        <v>60600</v>
       </c>
     </row>
     <row r="15">
@@ -1071,19 +1071,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>52340</v>
+        <v>52738</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>45740</v>
+        <v>46138</v>
       </c>
     </row>
     <row r="17">
@@ -1197,19 +1197,19 @@
         <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>39800</v>
+        <v>60920</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>5800</v>
+        <v>26920</v>
       </c>
     </row>
     <row r="20">
@@ -1461,19 +1461,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>9090</v>
+        <v>13070</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>12064</v>
+        <v>8084</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>64798</v>
+        <v>70376</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1511,11 +1511,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>55012</v>
+        <v>60590</v>
       </c>
     </row>
     <row r="27">
@@ -1659,19 +1659,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>37840</v>
+        <v>47800</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>25840</v>
+        <v>35800</v>
       </c>
     </row>
     <row r="31">
@@ -1701,31 +1701,31 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>127248</v>
+        <v>148204</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>13100</v>
+        <v>17080</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>114148</v>
+        <v>131124</v>
       </c>
     </row>
     <row r="32">
@@ -1743,31 +1743,31 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>48780</v>
+        <v>68700</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>48780</v>
+        <v>64720</v>
       </c>
     </row>
     <row r="33">
@@ -1785,31 +1785,31 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>21161</v>
+        <v>27761</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>16181</v>
+        <v>17801</v>
       </c>
     </row>
     <row r="34">
@@ -1827,19 +1827,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>42679</v>
+        <v>57619</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>42679</v>
+        <v>57619</v>
       </c>
     </row>
     <row r="35">
@@ -1869,19 +1869,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>23720</v>
+        <v>33680</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>23720</v>
+        <v>33680</v>
       </c>
     </row>
     <row r="36">
@@ -1911,19 +1911,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>35738</v>
+        <v>45698</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>31758</v>
+        <v>41718</v>
       </c>
     </row>
     <row r="37">
@@ -1953,19 +1953,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>14940</v>
+        <v>29880</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1973,11 +1973,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>10960</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="38">
@@ -1995,19 +1995,19 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1503.6%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>-85708</v>
+        <v>-80008</v>
       </c>
     </row>
     <row r="39">
